--- a/public/exports/29189609.xlsx
+++ b/public/exports/29189609.xlsx
@@ -481,16 +481,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805508</t>
+          <t xml:space="preserve">335014</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F10">
-        <v>995</v>
+        <v>1514</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -531,16 +531,16 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805508</t>
+          <t xml:space="preserve">335014</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F11">
-        <v>1395</v>
+        <v>917</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -581,16 +581,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805508</t>
+          <t xml:space="preserve">337871, 337872</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F12">
-        <v>2716</v>
+        <v>399</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">4414216</t>
+          <t xml:space="preserve">338782</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="F13">
-        <v>935</v>
+        <v>655</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">4414216</t>
+          <t xml:space="preserve">338782</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="F14">
-        <v>960</v>
+        <v>262</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">4414216</t>
+          <t xml:space="preserve">338783</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="F15">
-        <v>448</v>
+        <v>749</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -786,11 +786,11 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F16">
-        <v>802</v>
+        <v>935</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -836,11 +836,11 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F17">
-        <v>993</v>
+        <v>960</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -881,16 +881,16 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">4416970, 100845205</t>
+          <t xml:space="preserve">4414216</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F18">
-        <v>318</v>
+        <v>448</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">4416989</t>
+          <t xml:space="preserve">4414216</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F19">
-        <v>855</v>
+        <v>802</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -981,16 +981,16 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">4417458</t>
+          <t xml:space="preserve">4414216</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F20">
-        <v>262</v>
+        <v>993</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1031,16 +1031,16 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">4417458</t>
+          <t xml:space="preserve">4416970, 100845205</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F21">
-        <v>276</v>
+        <v>318</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1081,16 +1081,16 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">4417458</t>
+          <t xml:space="preserve">4416989</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F22">
-        <v>256</v>
+        <v>855</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">4418448</t>
+          <t xml:space="preserve">4417458</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="F23">
-        <v>362</v>
+        <v>262</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1181,16 +1181,16 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">4418452</t>
+          <t xml:space="preserve">4417458</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F24">
-        <v>409</v>
+        <v>276</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1231,16 +1231,16 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419298</t>
+          <t xml:space="preserve">4417458</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F25">
-        <v>463</v>
+        <v>256</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1281,16 +1281,16 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419703</t>
+          <t xml:space="preserve">4418448</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F26">
-        <v>1259</v>
+        <v>362</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1331,16 +1331,16 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419703</t>
+          <t xml:space="preserve">4418452</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F27">
-        <v>1728</v>
+        <v>409</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419703</t>
+          <t xml:space="preserve">4419298</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F28">
-        <v>704</v>
+        <v>463</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1431,16 +1431,16 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419782</t>
+          <t xml:space="preserve">4419703</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F29">
-        <v>419</v>
+        <v>1259</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1481,16 +1481,16 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">4427587</t>
+          <t xml:space="preserve">4419703</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F30">
-        <v>3129</v>
+        <v>1728</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1531,16 +1531,16 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">4427587</t>
+          <t xml:space="preserve">4419703</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F31">
-        <v>1671</v>
+        <v>704</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">4427732</t>
+          <t xml:space="preserve">4427587</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="F32">
-        <v>502</v>
+        <v>3129</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1631,16 +1631,16 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">4468195</t>
+          <t xml:space="preserve">4427587</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F33">
-        <v>5216</v>
+        <v>1671</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1681,16 +1681,16 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">4468325</t>
+          <t xml:space="preserve">4427732</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F34">
-        <v>715</v>
+        <v>502</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1731,16 +1731,16 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">4468945</t>
+          <t xml:space="preserve">4468195</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F35">
-        <v>286</v>
+        <v>5216</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1781,16 +1781,16 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">4469018</t>
+          <t xml:space="preserve">4468325</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F36">
-        <v>2841</v>
+        <v>715</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1831,16 +1831,16 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">4469018</t>
+          <t xml:space="preserve">4468945</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F37">
-        <v>795</v>
+        <v>286</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1886,11 +1886,11 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F38">
-        <v>2194</v>
+        <v>2841</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1936,11 +1936,11 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F39">
-        <v>825</v>
+        <v>795</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1986,11 +1986,11 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F40">
-        <v>1037</v>
+        <v>2194</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2031,16 +2031,16 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">4471273</t>
+          <t xml:space="preserve">4469018</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F41">
-        <v>1021</v>
+        <v>825</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2081,16 +2081,16 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">4476997</t>
+          <t xml:space="preserve">4469018</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F42">
-        <v>698</v>
+        <v>1037</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2131,16 +2131,16 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">4476997</t>
+          <t xml:space="preserve">4471273</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F43">
-        <v>282</v>
+        <v>1021</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2186,11 +2186,11 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F44">
-        <v>1606</v>
+        <v>698</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2236,11 +2236,11 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F45">
-        <v>516</v>
+        <v>282</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2281,16 +2281,16 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">4477007</t>
+          <t xml:space="preserve">4476997</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F46">
-        <v>1725</v>
+        <v>1606</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2331,16 +2331,16 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">4479526</t>
+          <t xml:space="preserve">4476997</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F47">
-        <v>2394</v>
+        <v>516</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2381,16 +2381,16 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">4479526</t>
+          <t xml:space="preserve">4477007</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F48">
-        <v>277</v>
+        <v>1725</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2436,11 +2436,11 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F49">
-        <v>1269</v>
+        <v>2394</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">4480741</t>
+          <t xml:space="preserve">4479526</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="F50">
-        <v>468</v>
+        <v>277</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2531,16 +2531,16 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">4480741</t>
+          <t xml:space="preserve">4479526</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F51">
-        <v>2597</v>
+        <v>1269</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2581,16 +2581,16 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">4481040</t>
+          <t xml:space="preserve">4480741</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F52">
-        <v>2266</v>
+        <v>468</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2631,16 +2631,16 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">4481040</t>
+          <t xml:space="preserve">4480741</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F53">
-        <v>324</v>
+        <v>2597</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2686,11 +2686,11 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F54">
-        <v>672</v>
+        <v>2266</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2731,16 +2731,16 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">4482853</t>
+          <t xml:space="preserve">4481040</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F55">
-        <v>283</v>
+        <v>324</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2781,16 +2781,16 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">4484037</t>
+          <t xml:space="preserve">4481040</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F56">
-        <v>3152</v>
+        <v>672</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">4485364</t>
+          <t xml:space="preserve">4482853</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F57">
-        <v>400</v>
+        <v>283</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2881,16 +2881,16 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">4485364</t>
+          <t xml:space="preserve">4484037</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F58">
-        <v>800</v>
+        <v>3152</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2936,11 +2936,11 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F59">
-        <v>465</v>
+        <v>400</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2981,16 +2981,16 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">4486943</t>
+          <t xml:space="preserve">4485364</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F60">
-        <v>2175</v>
+        <v>800</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3031,16 +3031,16 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">4486943</t>
+          <t xml:space="preserve">4485364</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F61">
-        <v>362</v>
+        <v>465</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3081,12 +3081,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">4486943</t>
+          <t xml:space="preserve">500690, 500691, 7643983</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F62">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">500690, 500691, 7643983</t>
+          <t xml:space="preserve">5724727</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3140,7 +3140,7 @@
         </is>
       </c>
       <c r="F63">
-        <v>328</v>
+        <v>606</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5724727</t>
+          <t xml:space="preserve">5725532</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="F64">
-        <v>606</v>
+        <v>3304</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3231,16 +3231,16 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">5725421</t>
+          <t xml:space="preserve">5726680</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F65">
-        <v>474</v>
+        <v>2020</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3281,16 +3281,16 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">5725421</t>
+          <t xml:space="preserve">5727472</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F66">
-        <v>264</v>
+        <v>1828</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3331,16 +3331,16 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">5725532</t>
+          <t xml:space="preserve">5727472</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F67">
-        <v>3304</v>
+        <v>3600</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">5726680</t>
+          <t xml:space="preserve">5727627</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="F68">
-        <v>2020</v>
+        <v>391</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">5727472</t>
+          <t xml:space="preserve">5727990</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="F69">
-        <v>1828</v>
+        <v>1156</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3481,16 +3481,16 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">5727472</t>
+          <t xml:space="preserve">5727990</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F70">
-        <v>3600</v>
+        <v>260</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3531,16 +3531,16 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">5727627</t>
+          <t xml:space="preserve">5728673</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F71">
-        <v>391</v>
+        <v>316</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">5727990</t>
+          <t xml:space="preserve">5788084</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3590,7 +3590,7 @@
         </is>
       </c>
       <c r="F72">
-        <v>1156</v>
+        <v>370</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3631,16 +3631,16 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">5727990</t>
+          <t xml:space="preserve">5788086</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F73">
-        <v>260</v>
+        <v>1662</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3681,16 +3681,16 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">5728673</t>
+          <t xml:space="preserve">5788498</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F74">
-        <v>316</v>
+        <v>266</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3731,16 +3731,16 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">5788084</t>
+          <t xml:space="preserve">5788498</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F75">
-        <v>370</v>
+        <v>458</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">5788086</t>
+          <t xml:space="preserve">5789801</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3790,7 +3790,7 @@
         </is>
       </c>
       <c r="F76">
-        <v>1662</v>
+        <v>828</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3831,16 +3831,16 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">5788498</t>
+          <t xml:space="preserve">5790131</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F77">
-        <v>266</v>
+        <v>7967</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3881,16 +3881,16 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">5788498</t>
+          <t xml:space="preserve">5790253</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F78">
-        <v>458</v>
+        <v>825</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">5789801</t>
+          <t xml:space="preserve">5793356</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="F79">
-        <v>828</v>
+        <v>983</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3981,16 +3981,16 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">5790131</t>
+          <t xml:space="preserve">7089195</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F80">
-        <v>7967</v>
+        <v>378</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">5790253</t>
+          <t xml:space="preserve">7155670</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4040,7 +4040,7 @@
         </is>
       </c>
       <c r="F81">
-        <v>825</v>
+        <v>472</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -4081,16 +4081,16 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">5793356</t>
+          <t xml:space="preserve">7155670</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F82">
-        <v>983</v>
+        <v>447</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -4131,16 +4131,16 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">7089195</t>
+          <t xml:space="preserve">7155670</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F83">
-        <v>378</v>
+        <v>1502</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -4186,11 +4186,11 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F84">
-        <v>472</v>
+        <v>266</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -4236,11 +4236,11 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F85">
-        <v>447</v>
+        <v>273</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -4281,16 +4281,16 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">7155670</t>
+          <t xml:space="preserve">7155749</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F86">
-        <v>1502</v>
+        <v>446</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -4331,16 +4331,16 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">7155670</t>
+          <t xml:space="preserve">7155749</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F87">
-        <v>266</v>
+        <v>2955</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -4381,16 +4381,16 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">7155670</t>
+          <t xml:space="preserve">7155749</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F88">
-        <v>273</v>
+        <v>1777</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -4436,11 +4436,11 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F89">
-        <v>446</v>
+        <v>1496</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -4486,11 +4486,11 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F90">
-        <v>2955</v>
+        <v>1270</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -4536,11 +4536,11 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F91">
-        <v>1777</v>
+        <v>360</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -4581,16 +4581,16 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">7155749</t>
+          <t xml:space="preserve">7293381</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F92">
-        <v>1496</v>
+        <v>342</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -4631,16 +4631,16 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">7155749</t>
+          <t xml:space="preserve">746264, 4471745</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F93">
-        <v>1270</v>
+        <v>1396</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -4681,16 +4681,16 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">7155749</t>
+          <t xml:space="preserve">746264, 4471745</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F94">
-        <v>360</v>
+        <v>320</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -4731,16 +4731,16 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">7293381</t>
+          <t xml:space="preserve">746342, 4414222</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F95">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -4781,16 +4781,16 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">746264, 4471745</t>
+          <t xml:space="preserve">746437, 5725570</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F96">
-        <v>1396</v>
+        <v>355</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -4831,16 +4831,16 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">746264, 4471745</t>
+          <t xml:space="preserve">746438, 5725548</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F97">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -4881,16 +4881,16 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">746271, 4473222</t>
+          <t xml:space="preserve">746456, 5725275</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F98">
-        <v>2466</v>
+        <v>268</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -4931,16 +4931,16 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">746342, 4414222</t>
+          <t xml:space="preserve">746458, 8463679</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F99">
-        <v>353</v>
+        <v>375</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -4981,16 +4981,16 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">746429, 7780728</t>
+          <t xml:space="preserve">746471, 5725286</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F100">
-        <v>2534</v>
+        <v>1793</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -5031,16 +5031,16 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">746429, 7780728</t>
+          <t xml:space="preserve">746495, 5790131</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F101">
-        <v>1249</v>
+        <v>920</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -5081,16 +5081,16 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">746431, 5725289</t>
+          <t xml:space="preserve">746495, 5790131</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F102">
-        <v>2061</v>
+        <v>2717</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -5131,16 +5131,16 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">746437, 5725570</t>
+          <t xml:space="preserve">746495, 5790131</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F103">
-        <v>355</v>
+        <v>1531</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -5181,16 +5181,16 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">746438, 5725548</t>
+          <t xml:space="preserve">746495, 5790131</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F104">
-        <v>333</v>
+        <v>740</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -5231,16 +5231,16 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">746456, 5725275</t>
+          <t xml:space="preserve">746495, 5790131</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F105">
-        <v>268</v>
+        <v>3165</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -5281,16 +5281,16 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">746458, 8463679</t>
+          <t xml:space="preserve">746514, 4480243</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F106">
-        <v>375</v>
+        <v>2572</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -5331,16 +5331,16 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">746461, 5725289</t>
+          <t xml:space="preserve">746514, 4480243</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F107">
-        <v>1794</v>
+        <v>1285</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -5381,16 +5381,16 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">746471, 5725286</t>
+          <t xml:space="preserve">746560, 4480243</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F108">
-        <v>1793</v>
+        <v>294</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -5431,16 +5431,16 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">746486, 8918730</t>
+          <t xml:space="preserve">746593, 4483444</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F109">
-        <v>3892</v>
+        <v>610</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">746495, 5790131</t>
+          <t xml:space="preserve">746603, 10238250</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F110">
-        <v>920</v>
+        <v>1035</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -5531,16 +5531,16 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">746495, 5790131</t>
+          <t xml:space="preserve">746603, 10238250</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F111">
-        <v>2717</v>
+        <v>339</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -5581,16 +5581,16 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">746495, 5790131</t>
+          <t xml:space="preserve">746733, 9329112</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F112">
-        <v>1531</v>
+        <v>765</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -5631,16 +5631,16 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">746495, 5790131</t>
+          <t xml:space="preserve">7485457</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F113">
-        <v>740</v>
+        <v>2460</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -5681,16 +5681,16 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">746495, 5790131</t>
+          <t xml:space="preserve">7755094</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F114">
-        <v>3165</v>
+        <v>484</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -5731,16 +5731,16 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">746514, 4480243</t>
+          <t xml:space="preserve">7755094</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F115">
-        <v>2572</v>
+        <v>1056</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -5781,16 +5781,16 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">746514, 4480243</t>
+          <t xml:space="preserve">7755094</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="F116">
-        <v>1285</v>
+        <v>420</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -5831,16 +5831,16 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">746560, 4480243</t>
+          <t xml:space="preserve">7755094</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F117">
-        <v>294</v>
+        <v>1060</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -5881,16 +5881,16 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">746593, 4483444</t>
+          <t xml:space="preserve">7755094</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F118">
-        <v>610</v>
+        <v>1060</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -5931,16 +5931,16 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">746603, 10238250</t>
+          <t xml:space="preserve">7755094</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F119">
-        <v>1035</v>
+        <v>1060</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -5981,16 +5981,16 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">746603, 10238250</t>
+          <t xml:space="preserve">7771244</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F120">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -6031,16 +6031,16 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">746733, 9329112</t>
+          <t xml:space="preserve">7771244</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F121">
-        <v>765</v>
+        <v>312</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -6081,16 +6081,16 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">747187, 100073869</t>
+          <t xml:space="preserve">7771244</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F122">
-        <v>475</v>
+        <v>329</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">7485457</t>
+          <t xml:space="preserve">7879617</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6140,7 +6140,7 @@
         </is>
       </c>
       <c r="F123">
-        <v>2460</v>
+        <v>635</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -6181,16 +6181,16 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">7755094</t>
+          <t xml:space="preserve">8427851</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F124">
-        <v>484</v>
+        <v>8744</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">7755094</t>
+          <t xml:space="preserve">8427851</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -6240,7 +6240,7 @@
         </is>
       </c>
       <c r="F125">
-        <v>1056</v>
+        <v>1430</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -6281,16 +6281,16 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">7755094</t>
+          <t xml:space="preserve">8427851</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F126">
-        <v>420</v>
+        <v>2567</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -6331,16 +6331,16 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">7755094</t>
+          <t xml:space="preserve">8427851</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F127">
-        <v>1060</v>
+        <v>380</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -6381,16 +6381,16 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">7755094</t>
+          <t xml:space="preserve">8463678</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F128">
-        <v>1060</v>
+        <v>424</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -6431,16 +6431,16 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">7755094</t>
+          <t xml:space="preserve">8463749</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F129">
-        <v>1060</v>
+        <v>735</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -6481,16 +6481,16 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">7771244</t>
+          <t xml:space="preserve">8570394</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F130">
-        <v>325</v>
+        <v>664</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -6531,16 +6531,16 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">7771244</t>
+          <t xml:space="preserve">8570394</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F131">
-        <v>312</v>
+        <v>706</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -6581,16 +6581,16 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">7771244</t>
+          <t xml:space="preserve">8570394</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F132">
-        <v>329</v>
+        <v>1287</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -6631,16 +6631,16 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">7879617</t>
+          <t xml:space="preserve">8570394</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F133">
-        <v>635</v>
+        <v>3146</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -6681,16 +6681,16 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">8427851</t>
+          <t xml:space="preserve">8570394</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F134">
-        <v>8744</v>
+        <v>1066</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -6731,16 +6731,16 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">8427851</t>
+          <t xml:space="preserve">8570394</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F135">
-        <v>1430</v>
+        <v>585</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -6781,16 +6781,16 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">8427851</t>
+          <t xml:space="preserve">8918730</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="F136">
-        <v>2567</v>
+        <v>1946</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -6831,16 +6831,16 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">8427851</t>
+          <t xml:space="preserve">9037914</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F137">
-        <v>380</v>
+        <v>1284</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -6881,16 +6881,16 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463678</t>
+          <t xml:space="preserve">9177616</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F138">
-        <v>424</v>
+        <v>2728</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -6931,16 +6931,16 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463749</t>
+          <t xml:space="preserve">9177616</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F139">
-        <v>735</v>
+        <v>1122</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">8570394</t>
+          <t xml:space="preserve">9221919</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="F140">
-        <v>664</v>
+        <v>3757</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -7031,16 +7031,16 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">8570394</t>
+          <t xml:space="preserve">9320803</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F141">
-        <v>706</v>
+        <v>424</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -7081,16 +7081,16 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">8570394</t>
+          <t xml:space="preserve">9854127</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F142">
-        <v>1287</v>
+        <v>3927</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -7131,30 +7131,30 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">8570394</t>
+          <t xml:space="preserve">4480741</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F143">
-        <v>3146</v>
+        <v>2202</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200008078</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2018-10-09</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -7181,30 +7181,30 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">8570394</t>
+          <t xml:space="preserve">8369478</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F144">
-        <v>1066</v>
+        <v>377</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200010715</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-02-18</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -7231,30 +7231,30 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">8570394</t>
+          <t xml:space="preserve">5727592</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F145">
-        <v>585</v>
+        <v>821</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200010804</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-02-22</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -7281,30 +7281,30 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">8918730</t>
+          <t xml:space="preserve">5726357</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F146">
-        <v>1946</v>
+        <v>563</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200010845</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-02-23</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">9037914</t>
+          <t xml:space="preserve">5728667</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -7340,21 +7340,21 @@
         </is>
       </c>
       <c r="F147">
-        <v>1284</v>
+        <v>491</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200010944</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-02-25</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -7381,30 +7381,30 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">9177616</t>
+          <t xml:space="preserve">5726356</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F148">
-        <v>2728</v>
+        <v>680</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200010984</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-02-26</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -7431,30 +7431,30 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">9177616</t>
+          <t xml:space="preserve">4422741</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F149">
-        <v>1122</v>
+        <v>390</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200011821</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-03-25</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">9221919</t>
+          <t xml:space="preserve">5726355</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -7490,21 +7490,21 @@
         </is>
       </c>
       <c r="F150">
-        <v>3757</v>
+        <v>529</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200011832</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-03-25</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">9320803</t>
+          <t xml:space="preserve">5725086</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -7540,21 +7540,21 @@
         </is>
       </c>
       <c r="F151">
-        <v>424</v>
+        <v>746</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200011892</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-03-26</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -7594,17 +7594,17 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200011880</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-03-26</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -7631,30 +7631,30 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">9854127</t>
+          <t xml:space="preserve">4419782</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F153">
-        <v>3927</v>
+        <v>419</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200012873</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-04-27</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">4480741</t>
+          <t xml:space="preserve">8161686</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -7690,16 +7690,16 @@
         </is>
       </c>
       <c r="F154">
-        <v>2202</v>
+        <v>314</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">200008078</t>
+          <t xml:space="preserve">200012912</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018-10-09</t>
+          <t xml:space="preserve">2019-04-27</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">8369478</t>
+          <t xml:space="preserve">9430418</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -7740,16 +7740,16 @@
         </is>
       </c>
       <c r="F155">
-        <v>377</v>
+        <v>311</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">200010715</t>
+          <t xml:space="preserve">200012910</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-02-18</t>
+          <t xml:space="preserve">2019-04-27</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">5727592</t>
+          <t xml:space="preserve">5726882</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -7790,16 +7790,16 @@
         </is>
       </c>
       <c r="F156">
-        <v>821</v>
+        <v>253</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">200010804</t>
+          <t xml:space="preserve">200012988</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-02-22</t>
+          <t xml:space="preserve">2019-04-28</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">5726357</t>
+          <t xml:space="preserve">4483012</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -7840,16 +7840,16 @@
         </is>
       </c>
       <c r="F157">
-        <v>563</v>
+        <v>848</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">200010845</t>
+          <t xml:space="preserve">200012993</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-02-23</t>
+          <t xml:space="preserve">2019-04-29</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">5728667</t>
+          <t xml:space="preserve">5725537</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -7890,16 +7890,16 @@
         </is>
       </c>
       <c r="F158">
-        <v>491</v>
+        <v>1556</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">200010944</t>
+          <t xml:space="preserve">200013034</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-02-25</t>
+          <t xml:space="preserve">2019-04-29</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -7931,7 +7931,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">5726356</t>
+          <t xml:space="preserve">5792930</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -7940,16 +7940,16 @@
         </is>
       </c>
       <c r="F159">
-        <v>680</v>
+        <v>356</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">200010984</t>
+          <t xml:space="preserve">200013038</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-02-26</t>
+          <t xml:space="preserve">2019-04-29</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">4422741</t>
+          <t xml:space="preserve">9379331</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -7990,16 +7990,16 @@
         </is>
       </c>
       <c r="F160">
-        <v>390</v>
+        <v>1290</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">200011821</t>
+          <t xml:space="preserve">200013233</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-03-25</t>
+          <t xml:space="preserve">2019-05-04</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">5726355</t>
+          <t xml:space="preserve">9670777</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -8040,16 +8040,16 @@
         </is>
       </c>
       <c r="F161">
-        <v>529</v>
+        <v>2672</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">200011832</t>
+          <t xml:space="preserve">200014492</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-03-25</t>
+          <t xml:space="preserve">2019-06-03</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -8081,25 +8081,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">8427359</t>
+          <t xml:space="preserve">4468081</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F162">
-        <v>403</v>
+        <v>837</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">200011840</t>
+          <t xml:space="preserve">200014740</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-03-25</t>
+          <t xml:space="preserve">2019-06-09</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">5725086</t>
+          <t xml:space="preserve">5724668</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -8140,16 +8140,16 @@
         </is>
       </c>
       <c r="F163">
-        <v>746</v>
+        <v>380</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">200011892</t>
+          <t xml:space="preserve">200014705</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-03-26</t>
+          <t xml:space="preserve">2019-06-09</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">8161686</t>
+          <t xml:space="preserve">4468323</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -8190,16 +8190,16 @@
         </is>
       </c>
       <c r="F164">
-        <v>314</v>
+        <v>614</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">200012912</t>
+          <t xml:space="preserve">200015083</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-04-27</t>
+          <t xml:space="preserve">2019-06-16</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -8231,25 +8231,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">9430418</t>
+          <t xml:space="preserve">5725421</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F165">
-        <v>311</v>
+        <v>474</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">200012910</t>
+          <t xml:space="preserve">100124776</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-04-27</t>
+          <t xml:space="preserve">2019-06-22</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -8281,25 +8281,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">5726882</t>
+          <t xml:space="preserve">5725421</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F166">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">200012988</t>
+          <t xml:space="preserve">100124776</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-04-28</t>
+          <t xml:space="preserve">2019-06-22</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -8331,7 +8331,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">4483012</t>
+          <t xml:space="preserve">8043441</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -8340,16 +8340,16 @@
         </is>
       </c>
       <c r="F167">
-        <v>848</v>
+        <v>3650</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">200012993</t>
+          <t xml:space="preserve">200015550</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-04-29</t>
+          <t xml:space="preserve">2019-06-22</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">5725537</t>
+          <t xml:space="preserve">5788092</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -8390,16 +8390,16 @@
         </is>
       </c>
       <c r="F168">
-        <v>1556</v>
+        <v>284</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">200013034</t>
+          <t xml:space="preserve">200016205</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-04-29</t>
+          <t xml:space="preserve">2019-06-29</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -8431,25 +8431,25 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">5792930</t>
+          <t xml:space="preserve">1805508</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F169">
-        <v>356</v>
+        <v>995</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">200013038</t>
+          <t xml:space="preserve">200033020</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-04-29</t>
+          <t xml:space="preserve">2020-06-25</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -8481,25 +8481,25 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">9379331</t>
+          <t xml:space="preserve">1805508</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F170">
-        <v>1290</v>
+        <v>1395</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">200013233</t>
+          <t xml:space="preserve">200033020</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-05-04</t>
+          <t xml:space="preserve">2020-06-25</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -8531,25 +8531,25 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">9670777</t>
+          <t xml:space="preserve">1805508</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F171">
-        <v>2672</v>
+        <v>2716</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014492</t>
+          <t xml:space="preserve">200033020</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-03</t>
+          <t xml:space="preserve">2020-06-25</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">4421250</t>
+          <t xml:space="preserve">1805508</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -8590,16 +8590,16 @@
         </is>
       </c>
       <c r="F172">
-        <v>3316</v>
+        <v>756</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014523</t>
+          <t xml:space="preserve">200033989</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-04</t>
+          <t xml:space="preserve">2020-07-13</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -8631,25 +8631,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">4468081</t>
+          <t xml:space="preserve">1805508</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F173">
-        <v>837</v>
+        <v>1725</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014740</t>
+          <t xml:space="preserve">200033989</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-09</t>
+          <t xml:space="preserve">2020-07-13</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">5724668</t>
+          <t xml:space="preserve">5725835</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -8690,16 +8690,16 @@
         </is>
       </c>
       <c r="F174">
-        <v>380</v>
+        <v>2126</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014705</t>
+          <t xml:space="preserve">200054663</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-09</t>
+          <t xml:space="preserve">2021-11-09</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -8731,25 +8731,25 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">4468323</t>
+          <t xml:space="preserve">746271, 4473222</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F175">
-        <v>614</v>
+        <v>2466</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">200015083</t>
+          <t xml:space="preserve">200057628</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-16</t>
+          <t xml:space="preserve">2022-02-23</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">8043441</t>
+          <t xml:space="preserve">4480225</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -8790,16 +8790,16 @@
         </is>
       </c>
       <c r="F176">
-        <v>3650</v>
+        <v>3911</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">200015550</t>
+          <t xml:space="preserve">200058806</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-22</t>
+          <t xml:space="preserve">2022-04-12</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -8831,25 +8831,25 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">5788092</t>
+          <t xml:space="preserve">5793356</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F177">
-        <v>284</v>
+        <v>1346</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">200016205</t>
+          <t xml:space="preserve">310011917</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-29</t>
+          <t xml:space="preserve">2022-11-05</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805508</t>
+          <t xml:space="preserve">5787947</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -8890,16 +8890,16 @@
         </is>
       </c>
       <c r="F178">
-        <v>756</v>
+        <v>1199</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033989</t>
+          <t xml:space="preserve">310034028</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-13</t>
+          <t xml:space="preserve">2023-04-09</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -8931,25 +8931,25 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805508</t>
+          <t xml:space="preserve">5724799</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F179">
-        <v>1725</v>
+        <v>376</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033989</t>
+          <t xml:space="preserve">311138690</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-13</t>
+          <t xml:space="preserve">2024-07-08</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -8981,25 +8981,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">5725835</t>
+          <t xml:space="preserve">747187, 100073869</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F180">
-        <v>2126</v>
+        <v>475</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054663</t>
+          <t xml:space="preserve">311125157</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-11-09</t>
+          <t xml:space="preserve">2025-07-15</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">4480225</t>
+          <t xml:space="preserve">100065998</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -9040,16 +9040,16 @@
         </is>
       </c>
       <c r="F181">
-        <v>3911</v>
+        <v>898</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">200058806</t>
+          <t xml:space="preserve">311142678</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-04-12</t>
+          <t xml:space="preserve">2025-10-30</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -9081,25 +9081,25 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">5793356</t>
+          <t xml:space="preserve">7771244</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F182">
-        <v>1346</v>
+        <v>1089</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">310011917</t>
+          <t xml:space="preserve">311168902</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-11-05</t>
+          <t xml:space="preserve">2026-04-07</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -9131,25 +9131,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787947</t>
+          <t xml:space="preserve">746431, 5725289</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F183">
-        <v>1199</v>
+        <v>2061</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">310034028</t>
+          <t xml:space="preserve">311169247</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-04-09</t>
+          <t xml:space="preserve">2026-04-08</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -9181,25 +9181,25 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">5724799</t>
+          <t xml:space="preserve">746461, 5725289</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="F184">
-        <v>376</v>
+        <v>1794</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311138690</t>
+          <t xml:space="preserve">311169248</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-07-08</t>
+          <t xml:space="preserve">2026-04-08</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -9231,25 +9231,25 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">100065998</t>
+          <t xml:space="preserve">746429, 7780728</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="F185">
-        <v>898</v>
+        <v>2534</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311142678</t>
+          <t xml:space="preserve">311169524</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-30</t>
+          <t xml:space="preserve">2026-04-11</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -9281,25 +9281,25 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">7771244</t>
+          <t xml:space="preserve">746429, 7780728</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F186">
-        <v>1089</v>
+        <v>1249</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311168902</t>
+          <t xml:space="preserve">311169524</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-07</t>
+          <t xml:space="preserve">2026-04-11</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -9331,35 +9331,35 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">335014</t>
+          <t xml:space="preserve">746486, 8918730</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="F187">
-        <v>1514</v>
+        <v>3892</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260256</t>
+          <t xml:space="preserve">311169525</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-11</t>
+          <t xml:space="preserve">2026-04-11</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -9381,20 +9381,20 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">335014</t>
+          <t xml:space="preserve">9676000</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F188">
-        <v>917</v>
+        <v>1571</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260256</t>
+          <t xml:space="preserve">311260252</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">9676000</t>
+          <t xml:space="preserve">8463704</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -9440,16 +9440,16 @@
         </is>
       </c>
       <c r="F189">
-        <v>1571</v>
+        <v>740</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260252</t>
+          <t xml:space="preserve">311267431</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-11</t>
+          <t xml:space="preserve">2027-08-21</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -9486,11 +9486,11 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F190">
-        <v>740</v>
+        <v>1407</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
@@ -9536,11 +9536,11 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F191">
-        <v>1407</v>
+        <v>8851</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
@@ -9586,11 +9586,11 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F192">
-        <v>8851</v>
+        <v>3739</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
@@ -9631,25 +9631,25 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463704</t>
+          <t xml:space="preserve">4487058</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F193">
-        <v>3739</v>
+        <v>2298</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267431</t>
+          <t xml:space="preserve">311267783</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-21</t>
+          <t xml:space="preserve">2027-08-22</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -9681,7 +9681,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">4487058</t>
+          <t xml:space="preserve">7593289</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -9690,16 +9690,16 @@
         </is>
       </c>
       <c r="F194">
-        <v>2298</v>
+        <v>525</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267783</t>
+          <t xml:space="preserve">311288413</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-22</t>
+          <t xml:space="preserve">2027-12-12</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -9731,7 +9731,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t xml:space="preserve">7593289</t>
+          <t xml:space="preserve">4421250</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -9740,16 +9740,16 @@
         </is>
       </c>
       <c r="F195">
-        <v>525</v>
+        <v>3316</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267663</t>
+          <t xml:space="preserve">311311426</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-22</t>
+          <t xml:space="preserve">2028-05-01</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -9781,20 +9781,20 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">338783</t>
+          <t xml:space="preserve">5787986</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F196">
-        <v>749</v>
+        <v>2956</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311378684</t>
+          <t xml:space="preserve">311378687</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -9836,11 +9836,11 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F197">
-        <v>2956</v>
+        <v>1297</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -9886,11 +9886,11 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F198">
-        <v>1297</v>
+        <v>1261</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
@@ -9931,20 +9931,20 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787986</t>
+          <t xml:space="preserve">5792458</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F199">
-        <v>1261</v>
+        <v>620</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311378687</t>
+          <t xml:space="preserve">311378685</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t xml:space="preserve">5792458</t>
+          <t xml:space="preserve">4419661</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -9990,16 +9990,16 @@
         </is>
       </c>
       <c r="F200">
-        <v>620</v>
+        <v>2236</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311378685</t>
+          <t xml:space="preserve">311389424</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-23</t>
+          <t xml:space="preserve">2029-07-18</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -10036,15 +10036,15 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F201">
-        <v>2236</v>
+        <v>453</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311389424</t>
+          <t xml:space="preserve">311389426</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -10081,20 +10081,20 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419661</t>
+          <t xml:space="preserve">4466616</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F202">
-        <v>453</v>
+        <v>2185</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311389426</t>
+          <t xml:space="preserve">311389428</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -10131,7 +10131,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t xml:space="preserve">4466616</t>
+          <t xml:space="preserve">5726628</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -10140,11 +10140,11 @@
         </is>
       </c>
       <c r="F203">
-        <v>2185</v>
+        <v>1856</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311389428</t>
+          <t xml:space="preserve">311389421</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -10186,11 +10186,11 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F204">
-        <v>1856</v>
+        <v>2960</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
@@ -10236,11 +10236,11 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F205">
-        <v>2960</v>
+        <v>1091</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
@@ -10286,11 +10286,11 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F206">
-        <v>1091</v>
+        <v>380</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
@@ -10336,11 +10336,11 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F207">
-        <v>380</v>
+        <v>474</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
@@ -10386,11 +10386,11 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F208">
-        <v>474</v>
+        <v>447</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
@@ -10431,20 +10431,20 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">5726628</t>
+          <t xml:space="preserve">9690066</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F209">
-        <v>447</v>
+        <v>788</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311389421</t>
+          <t xml:space="preserve">311389420</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -10481,25 +10481,25 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690066</t>
+          <t xml:space="preserve">9722833</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F210">
-        <v>788</v>
+        <v>390</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311389420</t>
+          <t xml:space="preserve">311419877</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-18</t>
+          <t xml:space="preserve">2030-01-30</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -10531,25 +10531,25 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t xml:space="preserve">338782</t>
+          <t xml:space="preserve">9722833</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F211">
-        <v>655</v>
+        <v>390</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311391434</t>
+          <t xml:space="preserve">311420217</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-06</t>
+          <t xml:space="preserve">2030-01-31</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -10581,25 +10581,25 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t xml:space="preserve">338782</t>
+          <t xml:space="preserve">5789756</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F212">
-        <v>262</v>
+        <v>392</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311391434</t>
+          <t xml:space="preserve">311491269</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-06</t>
+          <t xml:space="preserve">2031-01-28</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -10631,25 +10631,25 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t xml:space="preserve">9722833</t>
+          <t xml:space="preserve">5789756</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F213">
-        <v>390</v>
+        <v>703</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311419877</t>
+          <t xml:space="preserve">311491269</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-30</t>
+          <t xml:space="preserve">2031-01-28</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -10681,25 +10681,25 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t xml:space="preserve">9722833</t>
+          <t xml:space="preserve">9701346</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F214">
-        <v>390</v>
+        <v>4482</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420217</t>
+          <t xml:space="preserve">311552774</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-31</t>
+          <t xml:space="preserve">2031-10-04</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t xml:space="preserve">337871, 337872</t>
+          <t xml:space="preserve">1477015</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -10740,16 +10740,16 @@
         </is>
       </c>
       <c r="F215">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424140</t>
+          <t xml:space="preserve">311554640</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-24</t>
+          <t xml:space="preserve">2031-10-12</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -10781,7 +10781,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t xml:space="preserve">5789756</t>
+          <t xml:space="preserve">8256077</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -10790,16 +10790,16 @@
         </is>
       </c>
       <c r="F216">
-        <v>392</v>
+        <v>1557</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311491269</t>
+          <t xml:space="preserve">311554630</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-28</t>
+          <t xml:space="preserve">2031-10-12</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -10831,25 +10831,25 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t xml:space="preserve">5789756</t>
+          <t xml:space="preserve">7755094</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F217">
-        <v>703</v>
+        <v>1060</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311491269</t>
+          <t xml:space="preserve">311555859</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-28</t>
+          <t xml:space="preserve">2031-10-18</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t xml:space="preserve">9701346</t>
+          <t xml:space="preserve">4419703</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -10890,16 +10890,16 @@
         </is>
       </c>
       <c r="F218">
-        <v>4482</v>
+        <v>606</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311552774</t>
+          <t xml:space="preserve">311561693</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-04</t>
+          <t xml:space="preserve">2031-11-13</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -10931,7 +10931,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t xml:space="preserve">1477015</t>
+          <t xml:space="preserve">4467758</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -10940,16 +10940,16 @@
         </is>
       </c>
       <c r="F219">
-        <v>417</v>
+        <v>401</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311554640</t>
+          <t xml:space="preserve">311599352</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-12</t>
+          <t xml:space="preserve">2032-02-10</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -10981,7 +10981,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t xml:space="preserve">8256077</t>
+          <t xml:space="preserve">100145225</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -10990,16 +10990,16 @@
         </is>
       </c>
       <c r="F220">
-        <v>1557</v>
+        <v>810</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311554630</t>
+          <t xml:space="preserve">311582272</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-12</t>
+          <t xml:space="preserve">2032-03-03</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t xml:space="preserve">7755094</t>
+          <t xml:space="preserve">4467959</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -11040,16 +11040,16 @@
         </is>
       </c>
       <c r="F221">
-        <v>1060</v>
+        <v>308</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555859</t>
+          <t xml:space="preserve">311598466</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-18</t>
+          <t xml:space="preserve">2032-05-06</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -11081,7 +11081,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419703</t>
+          <t xml:space="preserve">7662602</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -11090,16 +11090,16 @@
         </is>
       </c>
       <c r="F222">
-        <v>606</v>
+        <v>1817</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561693</t>
+          <t xml:space="preserve">311650708</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-13</t>
+          <t xml:space="preserve">2032-12-20</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -11131,7 +11131,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t xml:space="preserve">4467758</t>
+          <t xml:space="preserve">4486943</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -11140,16 +11140,16 @@
         </is>
       </c>
       <c r="F223">
-        <v>401</v>
+        <v>2175</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311599352</t>
+          <t xml:space="preserve">311679351</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-10</t>
+          <t xml:space="preserve">2033-05-09</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -11181,25 +11181,25 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t xml:space="preserve">100145225</t>
+          <t xml:space="preserve">4486943</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F224">
-        <v>810</v>
+        <v>362</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582272</t>
+          <t xml:space="preserve">311679351</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-03</t>
+          <t xml:space="preserve">2033-05-09</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -11231,25 +11231,25 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t xml:space="preserve">4467959</t>
+          <t xml:space="preserve">4486943</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F225">
-        <v>308</v>
+        <v>328</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311598466</t>
+          <t xml:space="preserve">311679351</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-06</t>
+          <t xml:space="preserve">2033-05-09</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -11281,25 +11281,25 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t xml:space="preserve">7662602</t>
+          <t xml:space="preserve">8427359</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F226">
-        <v>1817</v>
+        <v>403</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650708</t>
+          <t xml:space="preserve">311679352</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-20</t>
+          <t xml:space="preserve">2033-05-09</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">

--- a/public/exports/29189609.xlsx
+++ b/public/exports/29189609.xlsx
@@ -91,17 +91,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 46</t>
+          <t xml:space="preserve">Aldershvilevej 16</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6940</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100020643</t>
+          <t xml:space="preserve">5726680</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -110,7 +110,7 @@
         </is>
       </c>
       <c r="H2">
-        <v>552</v>
+        <v>2020</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,17 +151,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallelvej 301</t>
+          <t xml:space="preserve">Birkevænget 31</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100060251</t>
+          <t xml:space="preserve">4479526</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -170,7 +170,7 @@
         </is>
       </c>
       <c r="H3">
-        <v>1021</v>
+        <v>2394</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,26 +211,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blomstermarken 9</t>
+          <t xml:space="preserve">Birkevænget 31</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">6971</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">100060556</t>
+          <t xml:space="preserve">4479526</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H4">
-        <v>890</v>
+        <v>277</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,26 +271,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 29</t>
+          <t xml:space="preserve">Birkevænget 31</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">100064416</t>
+          <t xml:space="preserve">4479526</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H5">
-        <v>1014</v>
+        <v>1269</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,7 +331,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lybækvej 14A</t>
+          <t xml:space="preserve">Birkmosevej 32</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -341,16 +341,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">10009013</t>
+          <t xml:space="preserve">5727990</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H6">
-        <v>406</v>
+        <v>1156</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,26 +391,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 48</t>
+          <t xml:space="preserve">Birkmosevej 32</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">100098945</t>
+          <t xml:space="preserve">5727990</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H7">
-        <v>1535</v>
+        <v>260</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,17 +451,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 50A</t>
+          <t xml:space="preserve">Blomstermarken 9</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6971</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">100287180</t>
+          <t xml:space="preserve">100060556</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="H8">
-        <v>340</v>
+        <v>890</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -511,17 +511,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørlundvej 3</t>
+          <t xml:space="preserve">Blomstervænget 51</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">100361476</t>
+          <t xml:space="preserve">5728673</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="H9">
-        <v>371</v>
+        <v>316</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -571,26 +571,26 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agersbækvej 15</t>
+          <t xml:space="preserve">Bredgade 120</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">335014</t>
+          <t xml:space="preserve">7755094</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H10">
-        <v>1514</v>
+        <v>484</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -631,17 +631,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agersbækvej 15</t>
+          <t xml:space="preserve">Bredgade 120</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">335014</t>
+          <t xml:space="preserve">7755094</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="H11">
-        <v>917</v>
+        <v>1056</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skjernåvej 4A</t>
+          <t xml:space="preserve">Bredgade 120</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">337871, 337872</t>
+          <t xml:space="preserve">7755094</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="H12">
-        <v>399</v>
+        <v>420</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -751,26 +751,26 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vardevej 45</t>
+          <t xml:space="preserve">Bredgade 120</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">338782</t>
+          <t xml:space="preserve">7755094</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H13">
-        <v>655</v>
+        <v>1060</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -811,26 +811,26 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vardevej 45</t>
+          <t xml:space="preserve">Bredgade 120</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">338782</t>
+          <t xml:space="preserve">7755094</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H14">
-        <v>262</v>
+        <v>1060</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -871,26 +871,26 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vardevej 45</t>
+          <t xml:space="preserve">Bredgade 120</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">338783</t>
+          <t xml:space="preserve">7755094</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H15">
-        <v>749</v>
+        <v>1060</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -931,17 +931,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gytjevej 70</t>
+          <t xml:space="preserve">Bryggen 1A</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6893</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">4414216</t>
+          <t xml:space="preserve">500690, 500691, 7643983</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="H16">
-        <v>935</v>
+        <v>328</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -991,26 +991,26 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gytjevej 70</t>
+          <t xml:space="preserve">Bækgårdsvej 33A</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">4414216</t>
+          <t xml:space="preserve">5790253</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H17">
-        <v>960</v>
+        <v>825</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gytjevej 70</t>
+          <t xml:space="preserve">Dalgasgade 50</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">4414216</t>
+          <t xml:space="preserve">4485364</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="H18">
-        <v>448</v>
+        <v>400</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gytjevej 70</t>
+          <t xml:space="preserve">Dalgasgade 50</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">4414216</t>
+          <t xml:space="preserve">4485364</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1130,7 +1130,7 @@
         </is>
       </c>
       <c r="H19">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1171,26 +1171,26 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gytjevej 70</t>
+          <t xml:space="preserve">Dalgasgade 50</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">4414216</t>
+          <t xml:space="preserve">4485364</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H20">
-        <v>993</v>
+        <v>465</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1231,26 +1231,26 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gytjevej 15</t>
+          <t xml:space="preserve">Dyrvigsvej 9</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">4416970, 100845205</t>
+          <t xml:space="preserve">4484037</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H21">
-        <v>318</v>
+        <v>3152</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1291,26 +1291,26 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 84</t>
+          <t xml:space="preserve">Enghavevej 10</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">4416989</t>
+          <t xml:space="preserve">8570394</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H22">
-        <v>855</v>
+        <v>706</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1351,26 +1351,26 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallelvej 116</t>
+          <t xml:space="preserve">Enghavevej 10</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">4417458</t>
+          <t xml:space="preserve">8570394</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H23">
-        <v>262</v>
+        <v>1287</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1411,26 +1411,26 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallelvej 116</t>
+          <t xml:space="preserve">Enghavevej 10</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">4417458</t>
+          <t xml:space="preserve">8570394</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H24">
-        <v>276</v>
+        <v>3146</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1471,26 +1471,26 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallelvej 116</t>
+          <t xml:space="preserve">Enghavevej 10</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">4417458</t>
+          <t xml:space="preserve">8570394</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H25">
-        <v>256</v>
+        <v>1066</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1531,26 +1531,26 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hoverdalvej 2</t>
+          <t xml:space="preserve">Enghavevej 10</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">6971</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">4418448</t>
+          <t xml:space="preserve">8570394</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H26">
-        <v>362</v>
+        <v>585</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hoverdalvej 4</t>
+          <t xml:space="preserve">Engtoften 1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">6971</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">4418452</t>
+          <t xml:space="preserve">5788086</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="H27">
-        <v>409</v>
+        <v>1662</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1651,17 +1651,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 34</t>
+          <t xml:space="preserve">Engvej 2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">6940</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419298</t>
+          <t xml:space="preserve">4468325</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="H28">
-        <v>463</v>
+        <v>715</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1711,26 +1711,26 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 34</t>
+          <t xml:space="preserve">Eskesensvej 1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">6940</t>
+          <t xml:space="preserve">6980</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419703</t>
+          <t xml:space="preserve">4427587</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H29">
-        <v>1259</v>
+        <v>3129</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1771,26 +1771,26 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 34</t>
+          <t xml:space="preserve">Eskesensvej 1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">6940</t>
+          <t xml:space="preserve">6980</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419703</t>
+          <t xml:space="preserve">4427587</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H30">
-        <v>1728</v>
+        <v>1671</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1831,26 +1831,26 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 34</t>
+          <t xml:space="preserve">Eskesensvej 14</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">6940</t>
+          <t xml:space="preserve">6980</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419703</t>
+          <t xml:space="preserve">7485457</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H31">
-        <v>704</v>
+        <v>2460</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1891,26 +1891,26 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eskesensvej 1</t>
+          <t xml:space="preserve">Fasers Led 2</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">6980</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">4427587</t>
+          <t xml:space="preserve">746438, 5725548</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H32">
-        <v>3129</v>
+        <v>333</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1951,26 +1951,26 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eskesensvej 1</t>
+          <t xml:space="preserve">Fasers Led 4</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">6980</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">4427587</t>
+          <t xml:space="preserve">9320803</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H33">
-        <v>1671</v>
+        <v>424</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2011,26 +2011,26 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fresiavej 4</t>
+          <t xml:space="preserve">Finderupsvej 7</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">6980</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">4427732</t>
+          <t xml:space="preserve">5788084</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H34">
-        <v>502</v>
+        <v>370</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2071,26 +2071,26 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lønborgvej 53</t>
+          <t xml:space="preserve">Finderupsvej 9</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">4468195</t>
+          <t xml:space="preserve">7771244</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H35">
-        <v>5216</v>
+        <v>325</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2131,26 +2131,26 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engvej 2</t>
+          <t xml:space="preserve">Finderupsvej 9</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">4468325</t>
+          <t xml:space="preserve">7771244</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H36">
-        <v>715</v>
+        <v>312</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2191,26 +2191,26 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vardevej 13</t>
+          <t xml:space="preserve">Finderupsvej 9</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">4468945</t>
+          <t xml:space="preserve">7771244</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H37">
-        <v>286</v>
+        <v>329</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2251,26 +2251,26 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vardevej 11</t>
+          <t xml:space="preserve">Fredensgade 34</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">4469018</t>
+          <t xml:space="preserve">5793356</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H38">
-        <v>2841</v>
+        <v>983</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2311,26 +2311,26 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vardevej 11</t>
+          <t xml:space="preserve">Fresiavej 4</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6980</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">4469018</t>
+          <t xml:space="preserve">4427732</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H39">
-        <v>795</v>
+        <v>502</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2371,26 +2371,26 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vardevej 11</t>
+          <t xml:space="preserve">Gl Kongevej 33</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">4469018</t>
+          <t xml:space="preserve">4482853</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H40">
-        <v>2194</v>
+        <v>283</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2431,26 +2431,26 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vardevej 11</t>
+          <t xml:space="preserve">Gl Kongevej 53A</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">4469018</t>
+          <t xml:space="preserve">7089195</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H41">
-        <v>825</v>
+        <v>378</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2491,26 +2491,26 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vardevej 11</t>
+          <t xml:space="preserve">Grønnegade 27</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">4469018</t>
+          <t xml:space="preserve">8463678</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H42">
-        <v>1037</v>
+        <v>424</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2551,26 +2551,26 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 2</t>
+          <t xml:space="preserve">Gytjevej 15</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">4471273</t>
+          <t xml:space="preserve">4416970, 100845205</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H43">
-        <v>1021</v>
+        <v>318</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2611,17 +2611,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 31A</t>
+          <t xml:space="preserve">Gytjevej 70</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">4476997</t>
+          <t xml:space="preserve">4414216</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="H44">
-        <v>698</v>
+        <v>935</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2671,26 +2671,26 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 31B</t>
+          <t xml:space="preserve">Gytjevej 70</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">4476997</t>
+          <t xml:space="preserve">4414216</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H45">
-        <v>282</v>
+        <v>960</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2731,26 +2731,26 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 31A</t>
+          <t xml:space="preserve">Gytjevej 70</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">4476997</t>
+          <t xml:space="preserve">4414216</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H46">
-        <v>1606</v>
+        <v>448</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2791,26 +2791,26 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 31A</t>
+          <t xml:space="preserve">Gytjevej 70</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">4476997</t>
+          <t xml:space="preserve">4414216</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H47">
-        <v>516</v>
+        <v>802</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2851,26 +2851,26 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 14</t>
+          <t xml:space="preserve">Gytjevej 70</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">4477007</t>
+          <t xml:space="preserve">4414216</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H48">
-        <v>1725</v>
+        <v>993</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2911,17 +2911,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkevænget 31</t>
+          <t xml:space="preserve">Halvejen 2</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6971</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">4479526</t>
+          <t xml:space="preserve">7155749</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="H49">
-        <v>2394</v>
+        <v>446</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2971,26 +2971,26 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkevænget 31</t>
+          <t xml:space="preserve">Halvejen 2</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6971</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">4479526</t>
+          <t xml:space="preserve">7155749</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H50">
-        <v>277</v>
+        <v>2955</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3031,26 +3031,26 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkevænget 31</t>
+          <t xml:space="preserve">Halvejen 2</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6971</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">4479526</t>
+          <t xml:space="preserve">7155749</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H51">
-        <v>1269</v>
+        <v>1777</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3091,26 +3091,26 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ternevej 2</t>
+          <t xml:space="preserve">Halvejen 2</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6971</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">4480741</t>
+          <t xml:space="preserve">7155749</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H52">
-        <v>468</v>
+        <v>1496</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3151,26 +3151,26 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ternevej 2</t>
+          <t xml:space="preserve">Halvejen 2</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6971</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">4480741</t>
+          <t xml:space="preserve">7155749</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H53">
-        <v>2597</v>
+        <v>1270</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3211,26 +3211,26 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkebyvej 65</t>
+          <t xml:space="preserve">Halvejen 2</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6971</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">4481040</t>
+          <t xml:space="preserve">7155749</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H54">
-        <v>2266</v>
+        <v>360</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3271,26 +3271,26 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkebyvej 65B</t>
+          <t xml:space="preserve">Henning Larsens Vej 9</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">4481040</t>
+          <t xml:space="preserve">746593, 4483444</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H55">
-        <v>324</v>
+        <v>610</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3331,26 +3331,26 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkebyvej 65</t>
+          <t xml:space="preserve">Holmegaardsvej 10</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">4481040</t>
+          <t xml:space="preserve">5727627</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H56">
-        <v>672</v>
+        <v>391</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3391,26 +3391,26 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Kongevej 33</t>
+          <t xml:space="preserve">Holmelunden 1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">4482853</t>
+          <t xml:space="preserve">9854127</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H57">
-        <v>283</v>
+        <v>3927</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3451,17 +3451,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyrvigsvej 9</t>
+          <t xml:space="preserve">Holmelunden 10</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">4484037</t>
+          <t xml:space="preserve">5727472</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3470,7 +3470,7 @@
         </is>
       </c>
       <c r="H58">
-        <v>3152</v>
+        <v>1828</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3511,26 +3511,26 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalgasgade 50</t>
+          <t xml:space="preserve">Holmelunden 11</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">4485364</t>
+          <t xml:space="preserve">5727472</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H59">
-        <v>400</v>
+        <v>3600</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3571,26 +3571,26 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalgasgade 50</t>
+          <t xml:space="preserve">Hoverdalvej 2</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6971</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">4485364</t>
+          <t xml:space="preserve">4418448</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H60">
-        <v>800</v>
+        <v>362</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3631,26 +3631,26 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalgasgade 50</t>
+          <t xml:space="preserve">Hoverdalvej 4</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6971</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">4485364</t>
+          <t xml:space="preserve">4418452</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H61">
-        <v>465</v>
+        <v>409</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3691,26 +3691,26 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bryggen 1A</t>
+          <t xml:space="preserve">Kibækvej 19</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">6893</t>
+          <t xml:space="preserve">6933</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">500690, 500691, 7643983</t>
+          <t xml:space="preserve">7293381</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H62">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3751,17 +3751,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvet 22</t>
+          <t xml:space="preserve">Kirkebyvej 65</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">5724727</t>
+          <t xml:space="preserve">4481040</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3770,7 +3770,7 @@
         </is>
       </c>
       <c r="H63">
-        <v>606</v>
+        <v>2266</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3811,26 +3811,26 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Fjorden 6</t>
+          <t xml:space="preserve">Kirkebyvej 65</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5725532</t>
+          <t xml:space="preserve">4481040</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H64">
-        <v>3304</v>
+        <v>672</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3871,26 +3871,26 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aldershvilevej 16</t>
+          <t xml:space="preserve">Kirkebyvej 65B</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">5726680</t>
+          <t xml:space="preserve">4481040</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H65">
-        <v>2020</v>
+        <v>324</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3931,17 +3931,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmelunden 10</t>
+          <t xml:space="preserve">Kirkegade 34</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6940</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">5727472</t>
+          <t xml:space="preserve">4419298</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="H66">
-        <v>1828</v>
+        <v>463</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3991,26 +3991,26 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmelunden 11</t>
+          <t xml:space="preserve">Kirkegade 46</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6940</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">5727472</t>
+          <t xml:space="preserve">100020643</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H67">
-        <v>3600</v>
+        <v>552</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -4051,17 +4051,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmegaardsvej 10</t>
+          <t xml:space="preserve">Kirkevej 14</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">5727627</t>
+          <t xml:space="preserve">4477007</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4070,7 +4070,7 @@
         </is>
       </c>
       <c r="H68">
-        <v>391</v>
+        <v>1725</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkmosevej 32</t>
+          <t xml:space="preserve">Kjærgaardsvej 7</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4121,16 +4121,16 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">5727990</t>
+          <t xml:space="preserve">8463749</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H69">
-        <v>1156</v>
+        <v>735</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -4171,17 +4171,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkmosevej 32</t>
+          <t xml:space="preserve">Klostervej 3</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">5727990</t>
+          <t xml:space="preserve">746264, 4471745</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4190,7 +4190,7 @@
         </is>
       </c>
       <c r="H70">
-        <v>260</v>
+        <v>1396</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -4231,26 +4231,26 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blomstervænget 51</t>
+          <t xml:space="preserve">Klostervej 3</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">5728673</t>
+          <t xml:space="preserve">746264, 4471745</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H71">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finderupsvej 7</t>
+          <t xml:space="preserve">Klostervej 65</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4301,16 +4301,16 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">5788084</t>
+          <t xml:space="preserve">8427851</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H72">
-        <v>370</v>
+        <v>2567</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engtoften 1</t>
+          <t xml:space="preserve">Klostervej 65</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4361,16 +4361,16 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">5788086</t>
+          <t xml:space="preserve">8427851</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H73">
-        <v>1662</v>
+        <v>380</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svinget 1G</t>
+          <t xml:space="preserve">Klostervej 67A</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4421,16 +4421,16 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">5788498</t>
+          <t xml:space="preserve">8427851</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H74">
-        <v>266</v>
+        <v>8744</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svinget 1G</t>
+          <t xml:space="preserve">Klostervej 67A</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4481,16 +4481,16 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">5788498</t>
+          <t xml:space="preserve">8427851</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H75">
-        <v>458</v>
+        <v>1430</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -4531,26 +4531,26 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tømrervej 2</t>
+          <t xml:space="preserve">Kroghedevej 2A</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6971</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">5789801</t>
+          <t xml:space="preserve">746603, 10238250</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H76">
-        <v>828</v>
+        <v>1035</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -4591,26 +4591,26 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ranunkelvej 7</t>
+          <t xml:space="preserve">Kroghedevej 2A</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6971</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">5790131</t>
+          <t xml:space="preserve">746603, 10238250</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H77">
-        <v>7967</v>
+        <v>339</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4651,26 +4651,26 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bækgårdsvej 33A</t>
+          <t xml:space="preserve">Lybækvej 14A</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">5790253</t>
+          <t xml:space="preserve">10009013</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H78">
-        <v>825</v>
+        <v>406</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4711,17 +4711,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensgade 34</t>
+          <t xml:space="preserve">Lønborgvej 53</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">5793356</t>
+          <t xml:space="preserve">4468195</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="H79">
-        <v>983</v>
+        <v>5216</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -4771,17 +4771,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Kongevej 53A</t>
+          <t xml:space="preserve">Mellemgade 23</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">7089195</t>
+          <t xml:space="preserve">8570394</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="H80">
-        <v>378</v>
+        <v>664</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4831,17 +4831,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolestræde 1</t>
+          <t xml:space="preserve">Nr Søndergårdsvej 1</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">6933</t>
+          <t xml:space="preserve">6971</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">7155670</t>
+          <t xml:space="preserve">746733, 9329112</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4850,7 +4850,7 @@
         </is>
       </c>
       <c r="H81">
-        <v>472</v>
+        <v>765</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4891,17 +4891,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolestræde 1</t>
+          <t xml:space="preserve">Nygade 48</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">6933</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">7155670</t>
+          <t xml:space="preserve">100098945</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="H82">
-        <v>447</v>
+        <v>1535</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4951,26 +4951,26 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolestræde 1</t>
+          <t xml:space="preserve">Nygade 50A</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">6933</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">7155670</t>
+          <t xml:space="preserve">100287180</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H83">
-        <v>1502</v>
+        <v>340</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -5011,26 +5011,26 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolestræde 1</t>
+          <t xml:space="preserve">Nørlundvej 3</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">6933</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">7155670</t>
+          <t xml:space="preserve">100361476</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H84">
-        <v>266</v>
+        <v>371</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -5071,26 +5071,26 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolestræde 1</t>
+          <t xml:space="preserve">Nørlundvej 7</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">6933</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">7155670</t>
+          <t xml:space="preserve">7879617</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H85">
-        <v>273</v>
+        <v>635</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -5131,17 +5131,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halvejen 2</t>
+          <t xml:space="preserve">Nørregade 84</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">6971</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">7155749</t>
+          <t xml:space="preserve">4416989</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5150,7 +5150,7 @@
         </is>
       </c>
       <c r="H86">
-        <v>446</v>
+        <v>855</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -5191,26 +5191,26 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halvejen 2</t>
+          <t xml:space="preserve">Nørregade 88</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">6971</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">7155749</t>
+          <t xml:space="preserve">746342, 4414222</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H87">
-        <v>2955</v>
+        <v>353</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -5251,26 +5251,26 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halvejen 2</t>
+          <t xml:space="preserve">Parallelvej 116</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">6971</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">7155749</t>
+          <t xml:space="preserve">4417458</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H88">
-        <v>1777</v>
+        <v>262</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -5311,26 +5311,26 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halvejen 2</t>
+          <t xml:space="preserve">Parallelvej 116</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">6971</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">7155749</t>
+          <t xml:space="preserve">4417458</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H89">
-        <v>1496</v>
+        <v>276</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -5371,26 +5371,26 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halvejen 2</t>
+          <t xml:space="preserve">Parallelvej 116</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">6971</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">7155749</t>
+          <t xml:space="preserve">4417458</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H90">
-        <v>1270</v>
+        <v>256</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -5431,26 +5431,26 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halvejen 2</t>
+          <t xml:space="preserve">Parallelvej 301</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">6971</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">7155749</t>
+          <t xml:space="preserve">100060251</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H91">
-        <v>360</v>
+        <v>1021</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -5491,26 +5491,26 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kibækvej 19</t>
+          <t xml:space="preserve">Ranunkelvej 1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">6933</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">7293381</t>
+          <t xml:space="preserve">746495, 5790131</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H92">
-        <v>342</v>
+        <v>920</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -5551,26 +5551,26 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostervej 3</t>
+          <t xml:space="preserve">Ranunkelvej 1</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">746264, 4471745</t>
+          <t xml:space="preserve">746495, 5790131</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H93">
-        <v>1396</v>
+        <v>2717</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -5611,26 +5611,26 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostervej 3</t>
+          <t xml:space="preserve">Ranunkelvej 1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">746264, 4471745</t>
+          <t xml:space="preserve">746495, 5790131</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H94">
-        <v>320</v>
+        <v>1531</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -5671,26 +5671,26 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 88</t>
+          <t xml:space="preserve">Ranunkelvej 1</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">746342, 4414222</t>
+          <t xml:space="preserve">746495, 5790131</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H95">
-        <v>353</v>
+        <v>3165</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -5731,26 +5731,26 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">V Strandsbjerg 29</t>
+          <t xml:space="preserve">Ranunkelvej 5</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">746437, 5725570</t>
+          <t xml:space="preserve">746495, 5790131</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H96">
-        <v>355</v>
+        <v>740</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -5791,26 +5791,26 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fasers Led 2</t>
+          <t xml:space="preserve">Ranunkelvej 7</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">746438, 5725548</t>
+          <t xml:space="preserve">5790131</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H97">
-        <v>333</v>
+        <v>7967</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -5851,26 +5851,26 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Fjorden 2A</t>
+          <t xml:space="preserve">Skolegade 34</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6940</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">746456, 5725275</t>
+          <t xml:space="preserve">4419703</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H98">
-        <v>268</v>
+        <v>1259</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -5911,26 +5911,26 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Fjorden 2B</t>
+          <t xml:space="preserve">Skolegade 34</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6940</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">746458, 8463679</t>
+          <t xml:space="preserve">4419703</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H99">
-        <v>375</v>
+        <v>1728</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -5971,26 +5971,26 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smed Sørensens Vej 3A</t>
+          <t xml:space="preserve">Skolegade 34</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6940</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">746471, 5725286</t>
+          <t xml:space="preserve">4419703</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H100">
-        <v>1793</v>
+        <v>704</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -6031,26 +6031,26 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ranunkelvej 1</t>
+          <t xml:space="preserve">Skolestræde 1</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6933</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">746495, 5790131</t>
+          <t xml:space="preserve">7155670</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H101">
-        <v>920</v>
+        <v>472</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -6091,26 +6091,26 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ranunkelvej 1</t>
+          <t xml:space="preserve">Skolestræde 1</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6933</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">746495, 5790131</t>
+          <t xml:space="preserve">7155670</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H102">
-        <v>2717</v>
+        <v>447</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -6151,26 +6151,26 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ranunkelvej 1</t>
+          <t xml:space="preserve">Skolestræde 1</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6933</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">746495, 5790131</t>
+          <t xml:space="preserve">7155670</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H103">
-        <v>1531</v>
+        <v>1502</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -6211,26 +6211,26 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ranunkelvej 5</t>
+          <t xml:space="preserve">Skolestræde 1</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6933</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">746495, 5790131</t>
+          <t xml:space="preserve">7155670</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H104">
-        <v>740</v>
+        <v>266</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -6271,26 +6271,26 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ranunkelvej 1</t>
+          <t xml:space="preserve">Skolestræde 1</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6933</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">746495, 5790131</t>
+          <t xml:space="preserve">7155670</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H105">
-        <v>3165</v>
+        <v>273</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -6331,17 +6331,17 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tylvadvej 2B</t>
+          <t xml:space="preserve">Skolevej 2</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">746514, 4480243</t>
+          <t xml:space="preserve">4471273</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -6350,7 +6350,7 @@
         </is>
       </c>
       <c r="H106">
-        <v>2572</v>
+        <v>1021</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tylvadvej 2B</t>
+          <t xml:space="preserve">Skolevænget 31A</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6401,16 +6401,16 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">746514, 4480243</t>
+          <t xml:space="preserve">4476997</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H107">
-        <v>1285</v>
+        <v>698</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tylvadvej 2C</t>
+          <t xml:space="preserve">Skolevænget 31A</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6461,16 +6461,16 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">746560, 4480243</t>
+          <t xml:space="preserve">4476997</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H108">
-        <v>294</v>
+        <v>1606</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -6511,26 +6511,26 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Henning Larsens Vej 9</t>
+          <t xml:space="preserve">Skolevænget 31A</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">746593, 4483444</t>
+          <t xml:space="preserve">4476997</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H109">
-        <v>610</v>
+        <v>516</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -6571,26 +6571,26 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kroghedevej 2A</t>
+          <t xml:space="preserve">Skolevænget 31B</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">6971</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">746603, 10238250</t>
+          <t xml:space="preserve">4476997</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H110">
-        <v>1035</v>
+        <v>282</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -6631,26 +6631,26 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kroghedevej 2A</t>
+          <t xml:space="preserve">Skovvej 29</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">6971</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">746603, 10238250</t>
+          <t xml:space="preserve">100064416</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H111">
-        <v>339</v>
+        <v>1014</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -6691,26 +6691,26 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nr Søndergårdsvej 1</t>
+          <t xml:space="preserve">Skyggehusvej 2A</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">6971</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">746733, 9329112</t>
+          <t xml:space="preserve">9177616</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H112">
-        <v>765</v>
+        <v>2728</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -6751,26 +6751,26 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eskesensvej 14</t>
+          <t xml:space="preserve">Skyggehusvej 2A</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">6980</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">7485457</t>
+          <t xml:space="preserve">9177616</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H113">
-        <v>2460</v>
+        <v>1122</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -6811,26 +6811,26 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 120</t>
+          <t xml:space="preserve">Smed Sørensens Vej 1</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">7755094</t>
+          <t xml:space="preserve">8918730</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="H114">
-        <v>484</v>
+        <v>1946</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -6871,26 +6871,26 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 120</t>
+          <t xml:space="preserve">Smed Sørensens Vej 3A</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">7755094</t>
+          <t xml:space="preserve">746471, 5725286</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H115">
-        <v>1056</v>
+        <v>1793</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -6931,26 +6931,26 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 120</t>
+          <t xml:space="preserve">Svinget 1G</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">7755094</t>
+          <t xml:space="preserve">5788498</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H116">
-        <v>420</v>
+        <v>266</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -6991,26 +6991,26 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 120</t>
+          <t xml:space="preserve">Svinget 1G</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">7755094</t>
+          <t xml:space="preserve">5788498</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H117">
-        <v>1060</v>
+        <v>458</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 120</t>
+          <t xml:space="preserve">Ternevej 2</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7061,16 +7061,16 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">7755094</t>
+          <t xml:space="preserve">4480741</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H118">
-        <v>1060</v>
+        <v>468</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 120</t>
+          <t xml:space="preserve">Ternevej 2</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7121,16 +7121,16 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">7755094</t>
+          <t xml:space="preserve">4480741</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H119">
-        <v>1060</v>
+        <v>2597</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -7171,26 +7171,26 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finderupsvej 9</t>
+          <t xml:space="preserve">Torvegade 20A</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">7771244</t>
+          <t xml:space="preserve">9037914</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H120">
-        <v>325</v>
+        <v>1284</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -7231,26 +7231,26 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finderupsvej 9</t>
+          <t xml:space="preserve">Torvet 22</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">7771244</t>
+          <t xml:space="preserve">5724727</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H121">
-        <v>312</v>
+        <v>606</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finderupsvej 9</t>
+          <t xml:space="preserve">Tylvadvej 2B</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7301,16 +7301,16 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">7771244</t>
+          <t xml:space="preserve">746514, 4480243</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H122">
-        <v>329</v>
+        <v>2572</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -7351,26 +7351,26 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørlundvej 7</t>
+          <t xml:space="preserve">Tylvadvej 2B</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">7879617</t>
+          <t xml:space="preserve">746514, 4480243</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H123">
-        <v>635</v>
+        <v>1285</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostervej 67A</t>
+          <t xml:space="preserve">Tylvadvej 2C</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7421,16 +7421,16 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">8427851</t>
+          <t xml:space="preserve">746560, 4480243</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H124">
-        <v>8744</v>
+        <v>294</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -7471,7 +7471,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostervej 67A</t>
+          <t xml:space="preserve">Tømrervej 2</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -7481,16 +7481,16 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">8427851</t>
+          <t xml:space="preserve">5789801</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H125">
-        <v>1430</v>
+        <v>828</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -7531,26 +7531,26 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostervej 65</t>
+          <t xml:space="preserve">V Strandsbjerg 29</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">8427851</t>
+          <t xml:space="preserve">746437, 5725570</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H126">
-        <v>2567</v>
+        <v>355</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -7591,26 +7591,26 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostervej 65</t>
+          <t xml:space="preserve">Vardevej 11</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">8427851</t>
+          <t xml:space="preserve">4469018</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H127">
-        <v>380</v>
+        <v>2841</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -7651,26 +7651,26 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnegade 27</t>
+          <t xml:space="preserve">Vardevej 11</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463678</t>
+          <t xml:space="preserve">4469018</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H128">
-        <v>424</v>
+        <v>795</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -7711,26 +7711,26 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjærgaardsvej 7</t>
+          <t xml:space="preserve">Vardevej 11</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463749</t>
+          <t xml:space="preserve">4469018</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H129">
-        <v>735</v>
+        <v>2194</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -7771,26 +7771,26 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mellemgade 23</t>
+          <t xml:space="preserve">Vardevej 11</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">8570394</t>
+          <t xml:space="preserve">4469018</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H130">
-        <v>664</v>
+        <v>825</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -7831,26 +7831,26 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 10</t>
+          <t xml:space="preserve">Vardevej 11</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">8570394</t>
+          <t xml:space="preserve">4469018</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H131">
-        <v>706</v>
+        <v>1037</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -7891,26 +7891,26 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 10</t>
+          <t xml:space="preserve">Vardevej 13</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">8570394</t>
+          <t xml:space="preserve">4468945</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H132">
-        <v>1287</v>
+        <v>286</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -7951,26 +7951,26 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 10</t>
+          <t xml:space="preserve">Ved Fjorden 2A</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">8570394</t>
+          <t xml:space="preserve">746456, 5725275</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H133">
-        <v>3146</v>
+        <v>268</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -8011,26 +8011,26 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 10</t>
+          <t xml:space="preserve">Ved Fjorden 2B</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">8570394</t>
+          <t xml:space="preserve">746458, 8463679</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H134">
-        <v>1066</v>
+        <v>375</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -8071,26 +8071,26 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 10</t>
+          <t xml:space="preserve">Ved Fjorden 6</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">8570394</t>
+          <t xml:space="preserve">5725532</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H135">
-        <v>585</v>
+        <v>3304</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
@@ -8131,26 +8131,26 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smed Sørensens Vej 1</t>
+          <t xml:space="preserve">Ågade 2</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">8918730</t>
+          <t xml:space="preserve">9221919</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H136">
-        <v>1946</v>
+        <v>3757</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
@@ -8191,17 +8191,17 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvegade 20A</t>
+          <t xml:space="preserve">Ternevej 2</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">9037914</t>
+          <t xml:space="preserve">4480741</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -8210,21 +8210,21 @@
         </is>
       </c>
       <c r="H137">
-        <v>1284</v>
+        <v>2202</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200008078</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2018-10-09</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -8251,40 +8251,40 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skyggehusvej 2A</t>
+          <t xml:space="preserve">Nørrevænget 33</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6933</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">9177616</t>
+          <t xml:space="preserve">8369478</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H138">
-        <v>2728</v>
+        <v>377</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200010715</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-02-18</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -8311,40 +8311,40 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skyggehusvej 2A</t>
+          <t xml:space="preserve">Vasevej 31</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">9177616</t>
+          <t xml:space="preserve">5727592</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H139">
-        <v>1122</v>
+        <v>821</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200010804</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-02-22</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -8371,17 +8371,17 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ågade 2</t>
+          <t xml:space="preserve">Søibergsvej 15</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">9221919</t>
+          <t xml:space="preserve">5726357</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -8390,21 +8390,21 @@
         </is>
       </c>
       <c r="H140">
-        <v>3757</v>
+        <v>563</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200010845</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-02-23</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fasers Led 4</t>
+          <t xml:space="preserve">Vasevej 29</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">9320803</t>
+          <t xml:space="preserve">5728667</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -8450,21 +8450,21 @@
         </is>
       </c>
       <c r="H141">
-        <v>424</v>
+        <v>491</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200010944</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-02-25</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmelunden 1</t>
+          <t xml:space="preserve">Søibergsvej 13</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -8501,30 +8501,30 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">9854127</t>
+          <t xml:space="preserve">5726356</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H142">
-        <v>3927</v>
+        <v>680</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200010984</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-02-26</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -8551,17 +8551,17 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ternevej 2</t>
+          <t xml:space="preserve">Klostervej 33</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">4480741</t>
+          <t xml:space="preserve">4422741</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -8570,16 +8570,16 @@
         </is>
       </c>
       <c r="H143">
-        <v>2202</v>
+        <v>390</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">200008078</t>
+          <t xml:space="preserve">200011821</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018-10-09</t>
+          <t xml:space="preserve">2019-03-25</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -8611,17 +8611,17 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrevænget 33</t>
+          <t xml:space="preserve">Søibergsvej 11</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">6933</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">8369478</t>
+          <t xml:space="preserve">5726355</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -8630,16 +8630,16 @@
         </is>
       </c>
       <c r="H144">
-        <v>377</v>
+        <v>529</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">200010720</t>
+          <t xml:space="preserve">200011832</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-02-18</t>
+          <t xml:space="preserve">2019-03-25</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -8671,35 +8671,35 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vasevej 31</t>
+          <t xml:space="preserve">Engdraget 28</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">5727592</t>
+          <t xml:space="preserve">9722833</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H145">
-        <v>821</v>
+        <v>520</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">200010804</t>
+          <t xml:space="preserve">200011880</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-02-22</t>
+          <t xml:space="preserve">2019-03-26</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søibergsvej 15</t>
+          <t xml:space="preserve">Godthaabsvej 8</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">5726357</t>
+          <t xml:space="preserve">5725086</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -8750,16 +8750,16 @@
         </is>
       </c>
       <c r="H146">
-        <v>563</v>
+        <v>746</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">200010845</t>
+          <t xml:space="preserve">200011892</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-02-23</t>
+          <t xml:space="preserve">2019-03-26</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -8791,17 +8791,17 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vasevej 29</t>
+          <t xml:space="preserve">Adelvej 39A</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6940</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">5728667</t>
+          <t xml:space="preserve">4419782</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -8810,16 +8810,16 @@
         </is>
       </c>
       <c r="H147">
-        <v>491</v>
+        <v>419</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">200010944</t>
+          <t xml:space="preserve">200012873</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-02-25</t>
+          <t xml:space="preserve">2019-04-27</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søibergsvej 13</t>
+          <t xml:space="preserve">Holmegaardsbakken 22</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">5726356</t>
+          <t xml:space="preserve">8161686</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -8870,16 +8870,16 @@
         </is>
       </c>
       <c r="H148">
-        <v>680</v>
+        <v>314</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">200010984</t>
+          <t xml:space="preserve">200012912</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-02-26</t>
+          <t xml:space="preserve">2019-04-27</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -8911,7 +8911,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostervej 33</t>
+          <t xml:space="preserve">Hvidkløvervej 8</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">4422741</t>
+          <t xml:space="preserve">9430418</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -8930,16 +8930,16 @@
         </is>
       </c>
       <c r="H149">
-        <v>390</v>
+        <v>311</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">200011821</t>
+          <t xml:space="preserve">200012910</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-03-25</t>
+          <t xml:space="preserve">2019-04-27</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søibergsvej 11</t>
+          <t xml:space="preserve">Herningvej 31</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5726355</t>
+          <t xml:space="preserve">5726882</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -8990,16 +8990,16 @@
         </is>
       </c>
       <c r="H150">
-        <v>529</v>
+        <v>253</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">200011832</t>
+          <t xml:space="preserve">200012988</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-03-25</t>
+          <t xml:space="preserve">2019-04-28</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Godthaabsvej 8</t>
+          <t xml:space="preserve">Byskellet 20</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">5725086</t>
+          <t xml:space="preserve">5725537</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -9050,16 +9050,16 @@
         </is>
       </c>
       <c r="H151">
-        <v>746</v>
+        <v>1556</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">200011892</t>
+          <t xml:space="preserve">200013034</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-03-26</t>
+          <t xml:space="preserve">2019-04-29</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -9091,35 +9091,35 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engdraget 28</t>
+          <t xml:space="preserve">Drosselvej 9</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">9722833</t>
+          <t xml:space="preserve">5792930</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H152">
-        <v>520</v>
+        <v>356</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">200011880</t>
+          <t xml:space="preserve">200013038</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-03-26</t>
+          <t xml:space="preserve">2019-04-29</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -9151,17 +9151,17 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adelvej 39A</t>
+          <t xml:space="preserve">Fischersvej 6</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t xml:space="preserve">6940</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419782</t>
+          <t xml:space="preserve">4483012</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -9170,16 +9170,16 @@
         </is>
       </c>
       <c r="H153">
-        <v>419</v>
+        <v>848</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">200012873</t>
+          <t xml:space="preserve">200012993</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-04-27</t>
+          <t xml:space="preserve">2019-04-29</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmegaardsbakken 22</t>
+          <t xml:space="preserve">Rødkløvervej 4</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">8161686</t>
+          <t xml:space="preserve">9379331</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -9230,16 +9230,16 @@
         </is>
       </c>
       <c r="H154">
-        <v>314</v>
+        <v>1290</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">200012912</t>
+          <t xml:space="preserve">200013233</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-04-27</t>
+          <t xml:space="preserve">2019-05-04</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidkløvervej 8</t>
+          <t xml:space="preserve">Klostervej 39</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">9430418</t>
+          <t xml:space="preserve">9670777</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -9290,16 +9290,16 @@
         </is>
       </c>
       <c r="H155">
-        <v>311</v>
+        <v>2672</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">200012910</t>
+          <t xml:space="preserve">200014492</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-04-27</t>
+          <t xml:space="preserve">2019-06-03</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herningvej 31</t>
+          <t xml:space="preserve">Kongevejen 1</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">5726882</t>
+          <t xml:space="preserve">5724668</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -9350,16 +9350,16 @@
         </is>
       </c>
       <c r="H156">
-        <v>253</v>
+        <v>380</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">200012988</t>
+          <t xml:space="preserve">200014705</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-04-28</t>
+          <t xml:space="preserve">2019-06-09</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -9391,17 +9391,17 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fischersvej 6</t>
+          <t xml:space="preserve">Lønhøjvej 38</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">4483012</t>
+          <t xml:space="preserve">4468081</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -9410,16 +9410,16 @@
         </is>
       </c>
       <c r="H157">
-        <v>848</v>
+        <v>837</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">200012993</t>
+          <t xml:space="preserve">200014740</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-04-29</t>
+          <t xml:space="preserve">2019-06-09</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -9451,17 +9451,17 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byskellet 20</t>
+          <t xml:space="preserve">Engdraget 4</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">5725537</t>
+          <t xml:space="preserve">4468323</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -9470,16 +9470,16 @@
         </is>
       </c>
       <c r="H158">
-        <v>1556</v>
+        <v>614</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">200013034</t>
+          <t xml:space="preserve">200015083</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-04-29</t>
+          <t xml:space="preserve">2019-06-16</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -9511,35 +9511,35 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drosselvej 9</t>
+          <t xml:space="preserve">Enghavevej 49</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">5792930</t>
+          <t xml:space="preserve">5725421</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H159">
-        <v>356</v>
+        <v>474</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">200013038</t>
+          <t xml:space="preserve">100124776</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-04-29</t>
+          <t xml:space="preserve">2019-06-22</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -9571,7 +9571,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rødkløvervej 4</t>
+          <t xml:space="preserve">Enghavevej 49</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -9581,25 +9581,25 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">9379331</t>
+          <t xml:space="preserve">5725421</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H160">
-        <v>1290</v>
+        <v>264</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">200013233</t>
+          <t xml:space="preserve">100124776</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-05-04</t>
+          <t xml:space="preserve">2019-06-22</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -9631,17 +9631,17 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostervej 39</t>
+          <t xml:space="preserve">Parallelvej 100</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">9670777</t>
+          <t xml:space="preserve">8043441</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -9650,16 +9650,16 @@
         </is>
       </c>
       <c r="H161">
-        <v>2672</v>
+        <v>3650</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014492</t>
+          <t xml:space="preserve">200015550</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-03</t>
+          <t xml:space="preserve">2019-06-22</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -9691,17 +9691,17 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lønhøjvej 38</t>
+          <t xml:space="preserve">Nylandsvej 10</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">4468081</t>
+          <t xml:space="preserve">5788092</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -9710,16 +9710,16 @@
         </is>
       </c>
       <c r="H162">
-        <v>837</v>
+        <v>284</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014740</t>
+          <t xml:space="preserve">200016205</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-09</t>
+          <t xml:space="preserve">2019-06-29</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -9751,35 +9751,35 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongevejen 1</t>
+          <t xml:space="preserve">Apoteker Rasmussens Plads 6A</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">5724668</t>
+          <t xml:space="preserve">1805508</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H163">
-        <v>380</v>
+        <v>995</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014705</t>
+          <t xml:space="preserve">200033020</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-09</t>
+          <t xml:space="preserve">2020-06-25</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engdraget 4</t>
+          <t xml:space="preserve">Apoteker Rasmussens Plads 6A</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -9821,25 +9821,25 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">4468323</t>
+          <t xml:space="preserve">1805508</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H164">
-        <v>614</v>
+        <v>1395</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">200015083</t>
+          <t xml:space="preserve">200033020</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-16</t>
+          <t xml:space="preserve">2020-06-25</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -9871,35 +9871,35 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 49</t>
+          <t xml:space="preserve">Kirkegade 3B</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">5725421</t>
+          <t xml:space="preserve">1805508</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H165">
-        <v>474</v>
+        <v>2716</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">100124776</t>
+          <t xml:space="preserve">200033020</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-22</t>
+          <t xml:space="preserve">2020-06-25</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -9931,35 +9931,35 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 49</t>
+          <t xml:space="preserve">Kirkegade 3B</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">5725421</t>
+          <t xml:space="preserve">1805508</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H166">
-        <v>264</v>
+        <v>756</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">100124776</t>
+          <t xml:space="preserve">200033989</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-22</t>
+          <t xml:space="preserve">2020-07-13</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -9991,35 +9991,35 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallelvej 100</t>
+          <t xml:space="preserve">Kirkegade 5</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">8043441</t>
+          <t xml:space="preserve">1805508</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H167">
-        <v>3650</v>
+        <v>1725</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">200015550</t>
+          <t xml:space="preserve">200033989</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-22</t>
+          <t xml:space="preserve">2020-07-13</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -10051,17 +10051,17 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nylandsvej 10</t>
+          <t xml:space="preserve">Kongevejen 52A</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">5788092</t>
+          <t xml:space="preserve">5725835</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -10070,16 +10070,16 @@
         </is>
       </c>
       <c r="H168">
-        <v>284</v>
+        <v>2126</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">200016205</t>
+          <t xml:space="preserve">200054663</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-29</t>
+          <t xml:space="preserve">2021-11-09</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -10111,35 +10111,35 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apoteker Rasmussens Plads 6A</t>
+          <t xml:space="preserve">Midtbyvej 32</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6893</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805508</t>
+          <t xml:space="preserve">746271, 4473222</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H169">
-        <v>995</v>
+        <v>2466</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033020</t>
+          <t xml:space="preserve">200057628</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-06-25</t>
+          <t xml:space="preserve">2022-02-23</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -10171,35 +10171,35 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apoteker Rasmussens Plads 6A</t>
+          <t xml:space="preserve">Tylvadvej 2A</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805508</t>
+          <t xml:space="preserve">4480225</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H170">
-        <v>1395</v>
+        <v>3911</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033020</t>
+          <t xml:space="preserve">200058806</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-06-25</t>
+          <t xml:space="preserve">2022-04-12</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -10231,35 +10231,35 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 3B</t>
+          <t xml:space="preserve">Fredensgade 28</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805508</t>
+          <t xml:space="preserve">5793356</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H171">
-        <v>2716</v>
+        <v>1346</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033020</t>
+          <t xml:space="preserve">310011917</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-06-25</t>
+          <t xml:space="preserve">2022-11-05</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -10291,17 +10291,17 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 3B</t>
+          <t xml:space="preserve">Tinghusvej 4</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805508</t>
+          <t xml:space="preserve">5787947</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -10310,16 +10310,16 @@
         </is>
       </c>
       <c r="H172">
-        <v>756</v>
+        <v>1199</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033989</t>
+          <t xml:space="preserve">310034028</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-13</t>
+          <t xml:space="preserve">2023-04-09</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -10351,35 +10351,35 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 5</t>
+          <t xml:space="preserve">Reberbanen 32</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805508</t>
+          <t xml:space="preserve">5724799</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H173">
-        <v>1725</v>
+        <v>376</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033989</t>
+          <t xml:space="preserve">311138690</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-13</t>
+          <t xml:space="preserve">2024-07-08</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -10411,35 +10411,35 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongevejen 52A</t>
+          <t xml:space="preserve">Østerbyvej 3B</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">5725835</t>
+          <t xml:space="preserve">747187, 100073869</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H174">
-        <v>2126</v>
+        <v>475</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054663</t>
+          <t xml:space="preserve">311125157</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-11-09</t>
+          <t xml:space="preserve">2025-07-15</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -10471,35 +10471,35 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midtbyvej 32</t>
+          <t xml:space="preserve">Holmegaardsbakken 4</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t xml:space="preserve">6893</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">746271, 4473222</t>
+          <t xml:space="preserve">100065998</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H175">
-        <v>2466</v>
+        <v>898</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057628</t>
+          <t xml:space="preserve">311142678</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-02-23</t>
+          <t xml:space="preserve">2025-10-30</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tylvadvej 2A</t>
+          <t xml:space="preserve">Finderupsvej 9</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">4480225</t>
+          <t xml:space="preserve">7771244</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -10550,16 +10550,16 @@
         </is>
       </c>
       <c r="H176">
-        <v>3911</v>
+        <v>1089</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">200058806</t>
+          <t xml:space="preserve">311168902</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-04-12</t>
+          <t xml:space="preserve">2026-04-07</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -10591,35 +10591,35 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensgade 28</t>
+          <t xml:space="preserve">Smed Sørensens Vej 3B</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">5793356</t>
+          <t xml:space="preserve">746431, 5725289</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H177">
-        <v>1346</v>
+        <v>2061</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">310011917</t>
+          <t xml:space="preserve">311169247</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-11-05</t>
+          <t xml:space="preserve">2026-04-08</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -10651,35 +10651,35 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tinghusvej 4</t>
+          <t xml:space="preserve">Smed Sørensens Vej 5</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787947</t>
+          <t xml:space="preserve">746461, 5725289</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="H178">
-        <v>1199</v>
+        <v>1794</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">310034028</t>
+          <t xml:space="preserve">311169248</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-04-09</t>
+          <t xml:space="preserve">2026-04-08</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reberbanen 32</t>
+          <t xml:space="preserve">E F Jacobsens Vej 7</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -10721,25 +10721,25 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">5724799</t>
+          <t xml:space="preserve">746486, 8918730</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="H179">
-        <v>376</v>
+        <v>3892</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311138690</t>
+          <t xml:space="preserve">311169525</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-07-08</t>
+          <t xml:space="preserve">2026-04-11</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -10771,35 +10771,35 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østerbyvej 3B</t>
+          <t xml:space="preserve">Smed Sørensens Vej 6</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">747187, 100073869</t>
+          <t xml:space="preserve">746429, 7780728</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="H180">
-        <v>475</v>
+        <v>2534</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311125157</t>
+          <t xml:space="preserve">311169524</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-07-15</t>
+          <t xml:space="preserve">2026-04-11</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -10831,7 +10831,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmegaardsbakken 4</t>
+          <t xml:space="preserve">Smed Sørensens Vej 6</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -10841,25 +10841,25 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">100065998</t>
+          <t xml:space="preserve">746429, 7780728</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="H181">
-        <v>898</v>
+        <v>1249</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311142678</t>
+          <t xml:space="preserve">311169524</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-30</t>
+          <t xml:space="preserve">2026-04-11</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -10891,17 +10891,17 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finderupsvej 9</t>
+          <t xml:space="preserve">Agersbækvej 15</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">7771244</t>
+          <t xml:space="preserve">335014</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -10910,26 +10910,26 @@
         </is>
       </c>
       <c r="H182">
-        <v>1089</v>
+        <v>1514</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311168902</t>
+          <t xml:space="preserve">311260256</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-07</t>
+          <t xml:space="preserve">2027-07-11</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -10951,7 +10951,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smed Sørensens Vej 3B</t>
+          <t xml:space="preserve">Agersbækvej 15</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -10961,35 +10961,35 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">746431, 5725289</t>
+          <t xml:space="preserve">335014</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H183">
-        <v>2061</v>
+        <v>917</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311169247</t>
+          <t xml:space="preserve">311260256</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-08</t>
+          <t xml:space="preserve">2027-07-11</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -11011,45 +11011,45 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smed Sørensens Vej 5</t>
+          <t xml:space="preserve">Algade 63</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6971</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">746461, 5725289</t>
+          <t xml:space="preserve">9676000</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H184">
-        <v>1794</v>
+        <v>1571</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311169248</t>
+          <t xml:space="preserve">311260252</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-08</t>
+          <t xml:space="preserve">2027-07-11</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -11071,7 +11071,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smed Sørensens Vej 6</t>
+          <t xml:space="preserve">Rindumvej 1</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -11081,35 +11081,35 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">746429, 7780728</t>
+          <t xml:space="preserve">8463704</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H185">
-        <v>2534</v>
+        <v>740</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311169524</t>
+          <t xml:space="preserve">311267431</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-11</t>
+          <t xml:space="preserve">2027-08-21</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -11131,7 +11131,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smed Sørensens Vej 6</t>
+          <t xml:space="preserve">Rindumvej 1</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11141,35 +11141,35 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">746429, 7780728</t>
+          <t xml:space="preserve">8463704</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H186">
-        <v>1249</v>
+        <v>1407</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311169524</t>
+          <t xml:space="preserve">311267431</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-11</t>
+          <t xml:space="preserve">2027-08-21</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">E F Jacobsens Vej 7</t>
+          <t xml:space="preserve">Rindumvej 1</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -11201,35 +11201,35 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">746486, 8918730</t>
+          <t xml:space="preserve">8463704</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H187">
-        <v>3892</v>
+        <v>8851</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311169525</t>
+          <t xml:space="preserve">311267431</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-11</t>
+          <t xml:space="preserve">2027-08-21</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -11251,35 +11251,35 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Algade 63</t>
+          <t xml:space="preserve">Rindumvej 1</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t xml:space="preserve">6971</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">9676000</t>
+          <t xml:space="preserve">8463704</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H188">
-        <v>1571</v>
+        <v>3739</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260252</t>
+          <t xml:space="preserve">311267431</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-11</t>
+          <t xml:space="preserve">2027-08-21</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -11311,17 +11311,17 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rindumvej 1</t>
+          <t xml:space="preserve">Bardevej 5</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463704</t>
+          <t xml:space="preserve">4487058</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -11330,16 +11330,16 @@
         </is>
       </c>
       <c r="H189">
-        <v>740</v>
+        <v>2298</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267431</t>
+          <t xml:space="preserve">311267783</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-21</t>
+          <t xml:space="preserve">2027-08-22</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -11371,35 +11371,35 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rindumvej 1</t>
+          <t xml:space="preserve">Ternevej 4</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463704</t>
+          <t xml:space="preserve">7593289</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H190">
-        <v>1407</v>
+        <v>525</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267431</t>
+          <t xml:space="preserve">311288413</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-21</t>
+          <t xml:space="preserve">2027-12-12</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -11431,7 +11431,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rindumvej 1</t>
+          <t xml:space="preserve">Klostervej 85</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -11441,25 +11441,25 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463704</t>
+          <t xml:space="preserve">4421250</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H191">
-        <v>8851</v>
+        <v>3316</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267431</t>
+          <t xml:space="preserve">311311426</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-21</t>
+          <t xml:space="preserve">2028-05-01</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -11491,35 +11491,35 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rindumvej 1</t>
+          <t xml:space="preserve">Mellemgade 8</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463704</t>
+          <t xml:space="preserve">5787986</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H192">
-        <v>3739</v>
+        <v>2956</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267431</t>
+          <t xml:space="preserve">311378687</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-21</t>
+          <t xml:space="preserve">2029-05-23</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -11551,35 +11551,35 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bardevej 5</t>
+          <t xml:space="preserve">Mellemgade 8</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">4487058</t>
+          <t xml:space="preserve">5787986</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H193">
-        <v>2298</v>
+        <v>1297</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267783</t>
+          <t xml:space="preserve">311378687</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-22</t>
+          <t xml:space="preserve">2029-05-23</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -11611,35 +11611,35 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ternevej 4</t>
+          <t xml:space="preserve">Mellemgade 8</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">7593289</t>
+          <t xml:space="preserve">5787986</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H194">
-        <v>525</v>
+        <v>1261</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288413</t>
+          <t xml:space="preserve">311378687</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-12</t>
+          <t xml:space="preserve">2029-05-23</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -11671,35 +11671,35 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostervej 85</t>
+          <t xml:space="preserve">Vardevej 45</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">4421250</t>
+          <t xml:space="preserve">338783</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H195">
-        <v>3316</v>
+        <v>749</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311311426</t>
+          <t xml:space="preserve">311378684</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-01</t>
+          <t xml:space="preserve">2029-05-23</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mellemgade 8</t>
+          <t xml:space="preserve">Vardevej 47A</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787986</t>
+          <t xml:space="preserve">5792458</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -11750,11 +11750,11 @@
         </is>
       </c>
       <c r="H196">
-        <v>2956</v>
+        <v>620</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311378687</t>
+          <t xml:space="preserve">311378685</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -11791,35 +11791,35 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mellemgade 8</t>
+          <t xml:space="preserve">Lunden 1</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6940</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787986</t>
+          <t xml:space="preserve">4419661</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H197">
-        <v>1297</v>
+        <v>2236</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311378687</t>
+          <t xml:space="preserve">311389424</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-23</t>
+          <t xml:space="preserve">2029-07-18</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -11851,35 +11851,35 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mellemgade 8</t>
+          <t xml:space="preserve">Lunden 1</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6940</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787986</t>
+          <t xml:space="preserve">4419661</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H198">
-        <v>1261</v>
+        <v>453</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311378687</t>
+          <t xml:space="preserve">311389426</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-23</t>
+          <t xml:space="preserve">2029-07-18</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -11911,35 +11911,35 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vardevej 47A</t>
+          <t xml:space="preserve">Skolevej 1</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">5792458</t>
+          <t xml:space="preserve">9690066</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H199">
-        <v>620</v>
+        <v>788</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311378685</t>
+          <t xml:space="preserve">311389420</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-23</t>
+          <t xml:space="preserve">2029-07-18</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -11971,17 +11971,17 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunden 1</t>
+          <t xml:space="preserve">Søibergsvej 3</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t xml:space="preserve">6940</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419661</t>
+          <t xml:space="preserve">5726628</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -11990,11 +11990,11 @@
         </is>
       </c>
       <c r="H200">
-        <v>2236</v>
+        <v>1856</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311389424</t>
+          <t xml:space="preserve">311389421</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -12031,30 +12031,30 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunden 1</t>
+          <t xml:space="preserve">Søibergsvej 3</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t xml:space="preserve">6940</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419661</t>
+          <t xml:space="preserve">5726628</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H201">
-        <v>453</v>
+        <v>2960</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311389426</t>
+          <t xml:space="preserve">311389421</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -12091,30 +12091,30 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tøstrupvej 26</t>
+          <t xml:space="preserve">Søibergsvej 3</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">4466616</t>
+          <t xml:space="preserve">5726628</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H202">
-        <v>2185</v>
+        <v>1091</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311389428</t>
+          <t xml:space="preserve">311389421</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -12166,11 +12166,11 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H203">
-        <v>1856</v>
+        <v>380</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
@@ -12226,11 +12226,11 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H204">
-        <v>2960</v>
+        <v>474</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
@@ -12286,11 +12286,11 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H205">
-        <v>1091</v>
+        <v>447</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
@@ -12331,30 +12331,30 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søibergsvej 3</t>
+          <t xml:space="preserve">Tøstrupvej 26</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">5726628</t>
+          <t xml:space="preserve">4466616</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H206">
-        <v>380</v>
+        <v>2185</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311389421</t>
+          <t xml:space="preserve">311389428</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -12391,35 +12391,35 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søibergsvej 3</t>
+          <t xml:space="preserve">Vardevej 45</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">5726628</t>
+          <t xml:space="preserve">338782</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H207">
-        <v>474</v>
+        <v>655</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311389421</t>
+          <t xml:space="preserve">311391434</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-18</t>
+          <t xml:space="preserve">2029-08-06</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -12451,35 +12451,35 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søibergsvej 3</t>
+          <t xml:space="preserve">Vardevej 45</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">5726628</t>
+          <t xml:space="preserve">338782</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H208">
-        <v>447</v>
+        <v>262</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311389421</t>
+          <t xml:space="preserve">311391434</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-18</t>
+          <t xml:space="preserve">2029-08-06</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -12511,35 +12511,35 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 1</t>
+          <t xml:space="preserve">Engdraget 24A</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690066</t>
+          <t xml:space="preserve">9722833</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H209">
-        <v>788</v>
+        <v>390</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311389420</t>
+          <t xml:space="preserve">311419877</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-18</t>
+          <t xml:space="preserve">2030-01-30</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -12571,7 +12571,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engdraget 24A</t>
+          <t xml:space="preserve">Engdraget 26A</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -12586,7 +12586,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H210">
@@ -12594,12 +12594,12 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311419880</t>
+          <t xml:space="preserve">311420217</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-30</t>
+          <t xml:space="preserve">2030-01-31</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engdraget 26A</t>
+          <t xml:space="preserve">Skjernåvej 4A</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -12641,25 +12641,25 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">9722833</t>
+          <t xml:space="preserve">337871, 337872</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H211">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420217</t>
+          <t xml:space="preserve">311424140</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-31</t>
+          <t xml:space="preserve">2030-02-24</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -12871,7 +12871,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lærkevænget 1</t>
+          <t xml:space="preserve">Jægervej 13</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -12881,7 +12881,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">1477015</t>
+          <t xml:space="preserve">8256077</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -12890,11 +12890,11 @@
         </is>
       </c>
       <c r="H215">
-        <v>417</v>
+        <v>1557</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311554640</t>
+          <t xml:space="preserve">311554630</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -12931,7 +12931,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jægervej 13</t>
+          <t xml:space="preserve">Lærkevænget 1</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">8256077</t>
+          <t xml:space="preserve">1477015</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -12950,11 +12950,11 @@
         </is>
       </c>
       <c r="H216">
-        <v>1557</v>
+        <v>417</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311554630</t>
+          <t xml:space="preserve">311554640</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -13351,30 +13351,30 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørlundvej 2</t>
+          <t xml:space="preserve">Agervej 4</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t xml:space="preserve">4486943</t>
+          <t xml:space="preserve">8427359</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H223">
-        <v>2175</v>
+        <v>403</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311679351</t>
+          <t xml:space="preserve">311679352</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -13426,11 +13426,11 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H224">
-        <v>362</v>
+        <v>2175</v>
       </c>
       <c r="I224" t="inlineStr">
         <is>
@@ -13486,11 +13486,11 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H225">
-        <v>328</v>
+        <v>362</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
@@ -13531,17 +13531,17 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agervej 4</t>
+          <t xml:space="preserve">Nørlundvej 2</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t xml:space="preserve">8427359</t>
+          <t xml:space="preserve">4486943</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -13550,11 +13550,11 @@
         </is>
       </c>
       <c r="H226">
-        <v>403</v>
+        <v>328</v>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311679352</t>
+          <t xml:space="preserve">311679351</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -14034,7 +14034,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892268</t>
+          <t xml:space="preserve">311892266</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -14071,17 +14071,17 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 10</t>
+          <t xml:space="preserve">Skolevej 2</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t xml:space="preserve">746506, 4477641</t>
+          <t xml:space="preserve">9690066</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -14090,11 +14090,11 @@
         </is>
       </c>
       <c r="H235">
-        <v>2072</v>
+        <v>2123</v>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892347</t>
+          <t xml:space="preserve">311892264</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -14131,30 +14131,30 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ågade 12</t>
+          <t xml:space="preserve">Skolevej 2</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t xml:space="preserve">9221920</t>
+          <t xml:space="preserve">9690066</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H236">
-        <v>729</v>
+        <v>915</v>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892262</t>
+          <t xml:space="preserve">311892264</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -14191,30 +14191,30 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ågade 14</t>
+          <t xml:space="preserve">Skolevej 2</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t xml:space="preserve">9221920</t>
+          <t xml:space="preserve">9690066</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H237">
-        <v>729</v>
+        <v>616</v>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892262</t>
+          <t xml:space="preserve">311892264</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -14266,11 +14266,11 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H238">
-        <v>2123</v>
+        <v>1810</v>
       </c>
       <c r="I238" t="inlineStr">
         <is>
@@ -14311,30 +14311,30 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 2</t>
+          <t xml:space="preserve">Stadionalle 10</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690066</t>
+          <t xml:space="preserve">746506, 4477641</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H239">
-        <v>915</v>
+        <v>2072</v>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892264</t>
+          <t xml:space="preserve">311892347</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -14371,30 +14371,30 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 2</t>
+          <t xml:space="preserve">Ågade 12</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690066</t>
+          <t xml:space="preserve">9221920</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H240">
-        <v>616</v>
+        <v>729</v>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892264</t>
+          <t xml:space="preserve">311892262</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -14431,30 +14431,30 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 2</t>
+          <t xml:space="preserve">Ågade 14</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690066</t>
+          <t xml:space="preserve">9221920</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H241">
-        <v>1810</v>
+        <v>729</v>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892264</t>
+          <t xml:space="preserve">311892262</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">

--- a/public/exports/29189609.xlsx
+++ b/public/exports/29189609.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L242"/>
+  <dimension ref="A1:M242"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -904,10 +974,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -964,10 +1039,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1024,10 +1104,15 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1084,10 +1169,15 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1144,10 +1234,15 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1204,10 +1299,15 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1264,10 +1364,15 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1324,10 +1429,15 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1384,10 +1494,15 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1444,10 +1559,15 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1504,10 +1624,15 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1564,10 +1689,15 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1624,10 +1754,15 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1684,10 +1819,15 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1744,10 +1884,15 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1804,10 +1949,15 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1864,10 +2014,15 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1924,10 +2079,15 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1984,10 +2144,15 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2044,10 +2209,15 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2104,10 +2274,15 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2164,10 +2339,15 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2224,10 +2404,15 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2284,10 +2469,15 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2344,10 +2534,15 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2404,10 +2599,15 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2464,10 +2664,15 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2524,10 +2729,15 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2584,10 +2794,15 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2644,10 +2859,15 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2704,10 +2924,15 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2764,10 +2989,15 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2824,10 +3054,15 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2884,10 +3119,15 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2944,10 +3184,15 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3004,10 +3249,15 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3064,10 +3314,15 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3124,10 +3379,15 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3184,10 +3444,15 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3244,10 +3509,15 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3304,10 +3574,15 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3364,10 +3639,15 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3424,10 +3704,15 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3484,10 +3769,15 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3544,10 +3834,15 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3604,10 +3899,15 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3664,10 +3964,15 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3724,10 +4029,15 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3784,10 +4094,15 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3844,10 +4159,15 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3904,10 +4224,15 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3964,10 +4289,15 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4024,10 +4354,15 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4084,10 +4419,15 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4144,10 +4484,15 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4204,10 +4549,15 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4264,10 +4614,15 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4324,10 +4679,15 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4384,10 +4744,15 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4444,10 +4809,15 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4504,10 +4874,15 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4564,10 +4939,15 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4624,10 +5004,15 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4684,10 +5069,15 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4744,10 +5134,15 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4804,10 +5199,15 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4864,10 +5264,15 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4924,10 +5329,15 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4984,10 +5394,15 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5044,10 +5459,15 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5104,10 +5524,15 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5164,10 +5589,15 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5224,10 +5654,15 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5284,10 +5719,15 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5344,10 +5784,15 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5404,10 +5849,15 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5464,10 +5914,15 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5524,10 +5979,15 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5584,10 +6044,15 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5644,10 +6109,15 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5704,10 +6174,15 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5764,10 +6239,15 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr">
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5824,10 +6304,15 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr">
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5884,10 +6369,15 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5944,10 +6434,15 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6004,10 +6499,15 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6064,10 +6564,15 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr">
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6124,10 +6629,15 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr">
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6184,10 +6694,15 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr">
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6244,10 +6759,15 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6304,10 +6824,15 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr">
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6364,10 +6889,15 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr">
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6424,10 +6954,15 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr">
+      <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6484,10 +7019,15 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr">
+      <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6544,10 +7084,15 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr">
+      <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6604,10 +7149,15 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr">
+      <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6664,10 +7214,15 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr">
+      <c r="M111" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6724,10 +7279,15 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr">
+      <c r="M112" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6784,10 +7344,15 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr">
+      <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6844,10 +7409,15 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr">
+      <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6904,10 +7474,15 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr">
+      <c r="M115" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6964,10 +7539,15 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr">
+      <c r="M116" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7024,10 +7604,15 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr">
+      <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7084,10 +7669,15 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr">
+      <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7144,10 +7734,15 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr">
+      <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7204,10 +7799,15 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr">
+      <c r="M120" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7264,10 +7864,15 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr">
+      <c r="M121" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7324,10 +7929,15 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr">
+      <c r="M122" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7384,10 +7994,15 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr">
+      <c r="M123" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7444,10 +8059,15 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr">
+      <c r="M124" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7504,10 +8124,15 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr">
+      <c r="M125" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7564,10 +8189,15 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr">
+      <c r="M126" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7624,10 +8254,15 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr">
+      <c r="M127" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7684,10 +8319,15 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr">
+      <c r="M128" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7744,10 +8384,15 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr">
+      <c r="M129" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7804,10 +8449,15 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr">
+      <c r="M130" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7864,10 +8514,15 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr">
+      <c r="M131" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7924,10 +8579,15 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr">
+      <c r="M132" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7984,10 +8644,15 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr">
+      <c r="M133" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8044,10 +8709,15 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr">
+      <c r="M134" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8104,10 +8774,15 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr">
+      <c r="M135" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8164,10 +8839,15 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr">
+      <c r="M136" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8219,15 +8899,20 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
+          <t xml:space="preserve">PP Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
           <t xml:space="preserve">2018-10-09</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
+      <c r="L137" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr">
+      <c r="M137" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8279,15 +8964,20 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-02-18</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
+      <c r="L138" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L138" t="inlineStr">
+      <c r="M138" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8339,15 +9029,20 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-02-22</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
+      <c r="L139" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr">
+      <c r="M139" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8399,15 +9094,20 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-02-23</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
+      <c r="L140" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L140" t="inlineStr">
+      <c r="M140" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8459,15 +9159,20 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-02-25</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
+      <c r="L141" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr">
+      <c r="M141" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8519,15 +9224,20 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-02-26</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
+      <c r="L142" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr">
+      <c r="M142" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8579,15 +9289,20 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-03-25</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
+      <c r="L143" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L143" t="inlineStr">
+      <c r="M143" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8639,15 +9354,20 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-03-25</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
+      <c r="L144" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr">
+      <c r="M144" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8699,15 +9419,20 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-03-26</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
+      <c r="L145" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L145" t="inlineStr">
+      <c r="M145" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8759,15 +9484,20 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-03-26</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
+      <c r="L146" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L146" t="inlineStr">
+      <c r="M146" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8819,15 +9549,20 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-04-27</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
+      <c r="L147" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L147" t="inlineStr">
+      <c r="M147" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8879,15 +9614,20 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-04-27</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
+      <c r="L148" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr">
+      <c r="M148" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8939,15 +9679,20 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-04-27</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
+      <c r="L149" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L149" t="inlineStr">
+      <c r="M149" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8999,15 +9744,20 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-04-28</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
+      <c r="L150" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L150" t="inlineStr">
+      <c r="M150" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9059,15 +9809,20 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-04-29</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
+      <c r="L151" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L151" t="inlineStr">
+      <c r="M151" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9119,15 +9874,20 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-04-29</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
+      <c r="L152" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L152" t="inlineStr">
+      <c r="M152" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9179,15 +9939,20 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-04-29</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
+      <c r="L153" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L153" t="inlineStr">
+      <c r="M153" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9239,15 +10004,20 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-05-04</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
+      <c r="L154" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L154" t="inlineStr">
+      <c r="M154" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9299,15 +10069,20 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-06-03</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
+      <c r="L155" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L155" t="inlineStr">
+      <c r="M155" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9359,15 +10134,20 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-06-09</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
+      <c r="L156" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L156" t="inlineStr">
+      <c r="M156" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9419,15 +10199,20 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-06-09</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
+      <c r="L157" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr">
+      <c r="M157" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9479,15 +10264,20 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-06-16</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
+      <c r="L158" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L158" t="inlineStr">
+      <c r="M158" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9539,15 +10329,20 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
+          <t xml:space="preserve">Holstebro Arkitektkontor ApS</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-06-22</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
+      <c r="L159" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L159" t="inlineStr">
+      <c r="M159" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9599,15 +10394,20 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
+          <t xml:space="preserve">Holstebro Arkitektkontor ApS</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-06-22</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
+      <c r="L160" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L160" t="inlineStr">
+      <c r="M160" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9659,15 +10459,20 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-06-22</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
+      <c r="L161" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L161" t="inlineStr">
+      <c r="M161" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9719,15 +10524,20 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-06-29</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
+      <c r="L162" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L162" t="inlineStr">
+      <c r="M162" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9779,15 +10589,20 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-06-25</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
+      <c r="L163" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L163" t="inlineStr">
+      <c r="M163" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9839,15 +10654,20 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-06-25</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
+      <c r="L164" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L164" t="inlineStr">
+      <c r="M164" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9899,15 +10719,20 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-06-25</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
+      <c r="L165" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L165" t="inlineStr">
+      <c r="M165" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9959,15 +10784,20 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-07-13</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
+      <c r="L166" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L166" t="inlineStr">
+      <c r="M166" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10019,15 +10849,20 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-07-13</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
+      <c r="L167" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L167" t="inlineStr">
+      <c r="M167" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10079,15 +10914,20 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-11-09</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr">
+      <c r="L168" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr">
+      <c r="M168" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10139,15 +10979,20 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Odense a/s</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-02-23</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
+      <c r="L169" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L169" t="inlineStr">
+      <c r="M169" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10199,15 +11044,20 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiMidt</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-04-12</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
+      <c r="L170" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L170" t="inlineStr">
+      <c r="M170" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10259,15 +11109,20 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Center Sydvestjylland</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-11-05</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
+      <c r="L171" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L171" t="inlineStr">
+      <c r="M171" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10319,15 +11174,20 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Skive</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-04-09</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
+      <c r="L172" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L172" t="inlineStr">
+      <c r="M172" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10379,15 +11239,20 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-07-08</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
+      <c r="L173" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L173" t="inlineStr">
+      <c r="M173" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10439,15 +11304,20 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-07-15</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
+      <c r="L174" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr">
+      <c r="M174" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10499,15 +11369,20 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-10-30</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
+      <c r="L175" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L175" t="inlineStr">
+      <c r="M175" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10559,15 +11434,20 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-04-07</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
+      <c r="L176" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L176" t="inlineStr">
+      <c r="M176" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10619,15 +11499,20 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-04-08</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
+      <c r="L177" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L177" t="inlineStr">
+      <c r="M177" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10679,15 +11564,20 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-04-08</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
+      <c r="L178" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L178" t="inlineStr">
+      <c r="M178" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10739,15 +11629,20 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-04-11</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
+      <c r="L179" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L179" t="inlineStr">
+      <c r="M179" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10799,15 +11694,20 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-04-11</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
+      <c r="L180" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L180" t="inlineStr">
+      <c r="M180" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10859,15 +11759,20 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-04-11</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
+      <c r="L181" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L181" t="inlineStr">
+      <c r="M181" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10919,15 +11824,20 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-11</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
+      <c r="L182" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L182" t="inlineStr">
+      <c r="M182" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10979,15 +11889,20 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-11</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr">
+      <c r="L183" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L183" t="inlineStr">
+      <c r="M183" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11039,15 +11954,20 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-11</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
+      <c r="L184" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L184" t="inlineStr">
+      <c r="M184" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11099,15 +12019,20 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-21</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr">
+      <c r="L185" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L185" t="inlineStr">
+      <c r="M185" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11159,15 +12084,20 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-21</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr">
+      <c r="L186" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L186" t="inlineStr">
+      <c r="M186" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11219,15 +12149,20 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-21</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr">
+      <c r="L187" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L187" t="inlineStr">
+      <c r="M187" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11279,15 +12214,20 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-21</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr">
+      <c r="L188" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L188" t="inlineStr">
+      <c r="M188" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11339,15 +12279,20 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-22</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr">
+      <c r="L189" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L189" t="inlineStr">
+      <c r="M189" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11399,15 +12344,20 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Center Midt- og Vestjylland</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-12</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr">
+      <c r="L190" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L190" t="inlineStr">
+      <c r="M190" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11459,15 +12409,20 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-05-01</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr">
+      <c r="L191" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L191" t="inlineStr">
+      <c r="M191" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11519,15 +12474,20 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-05-23</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr">
+      <c r="L192" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L192" t="inlineStr">
+      <c r="M192" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11579,15 +12539,20 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-05-23</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr">
+      <c r="L193" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L193" t="inlineStr">
+      <c r="M193" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11639,15 +12604,20 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-05-23</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr">
+      <c r="L194" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L194" t="inlineStr">
+      <c r="M194" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11699,15 +12669,20 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-05-23</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr">
+      <c r="L195" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L195" t="inlineStr">
+      <c r="M195" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11759,15 +12734,20 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-05-23</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr">
+      <c r="L196" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L196" t="inlineStr">
+      <c r="M196" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11819,15 +12799,20 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-07-18</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr">
+      <c r="L197" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L197" t="inlineStr">
+      <c r="M197" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11879,15 +12864,20 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-07-18</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr">
+      <c r="L198" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L198" t="inlineStr">
+      <c r="M198" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11939,15 +12929,20 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-07-18</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr">
+      <c r="L199" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L199" t="inlineStr">
+      <c r="M199" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11999,15 +12994,20 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-07-18</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr">
+      <c r="L200" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L200" t="inlineStr">
+      <c r="M200" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12059,15 +13059,20 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-07-18</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
+      <c r="L201" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L201" t="inlineStr">
+      <c r="M201" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12119,15 +13124,20 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-07-18</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
+      <c r="L202" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L202" t="inlineStr">
+      <c r="M202" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12179,15 +13189,20 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-07-18</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
+      <c r="L203" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L203" t="inlineStr">
+      <c r="M203" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12239,15 +13254,20 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-07-18</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr">
+      <c r="L204" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L204" t="inlineStr">
+      <c r="M204" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12299,15 +13319,20 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-07-18</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
+      <c r="L205" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L205" t="inlineStr">
+      <c r="M205" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12359,15 +13384,20 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-07-18</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr">
+      <c r="L206" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L206" t="inlineStr">
+      <c r="M206" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12419,15 +13449,20 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-06</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr">
+      <c r="L207" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L207" t="inlineStr">
+      <c r="M207" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12479,15 +13514,20 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-06</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr">
+      <c r="L208" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L208" t="inlineStr">
+      <c r="M208" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12534,20 +13574,25 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311419877</t>
+          <t xml:space="preserve">311419880</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-30</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
+      <c r="L209" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L209" t="inlineStr">
+      <c r="M209" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12599,15 +13644,20 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-31</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr">
+      <c r="L210" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L210" t="inlineStr">
+      <c r="M210" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12659,15 +13709,20 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
+          <t xml:space="preserve">Scanenergi A/S</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-02-24</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
+      <c r="L211" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L211" t="inlineStr">
+      <c r="M211" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12719,15 +13774,20 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-01-28</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr">
+      <c r="L212" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L212" t="inlineStr">
+      <c r="M212" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12779,15 +13839,20 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-01-28</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr">
+      <c r="L213" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L213" t="inlineStr">
+      <c r="M213" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12839,15 +13904,20 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-04</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr">
+      <c r="L214" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L214" t="inlineStr">
+      <c r="M214" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12899,15 +13969,20 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-12</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr">
+      <c r="L215" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L215" t="inlineStr">
+      <c r="M215" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12959,15 +14034,20 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-12</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr">
+      <c r="L216" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L216" t="inlineStr">
+      <c r="M216" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13019,15 +14099,20 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-18</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr">
+      <c r="L217" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L217" t="inlineStr">
+      <c r="M217" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13079,15 +14164,20 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-13</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr">
+      <c r="L218" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L218" t="inlineStr">
+      <c r="M218" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13139,15 +14229,20 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-02-10</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr">
+      <c r="L219" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L219" t="inlineStr">
+      <c r="M219" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13199,15 +14294,20 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-03</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr">
+      <c r="L220" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L220" t="inlineStr">
+      <c r="M220" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13259,15 +14359,20 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-06</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr">
+      <c r="L221" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L221" t="inlineStr">
+      <c r="M221" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13319,15 +14424,20 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
+          <t xml:space="preserve">MST-Bygtjek ApS</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-20</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr">
+      <c r="L222" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L222" t="inlineStr">
+      <c r="M222" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13379,15 +14489,20 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-09</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr">
+      <c r="L223" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L223" t="inlineStr">
+      <c r="M223" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13439,15 +14554,20 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-09</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr">
+      <c r="L224" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L224" t="inlineStr">
+      <c r="M224" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13499,15 +14619,20 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-09</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr">
+      <c r="L225" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L225" t="inlineStr">
+      <c r="M225" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13559,15 +14684,20 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-09</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr">
+      <c r="L226" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L226" t="inlineStr">
+      <c r="M226" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13619,15 +14749,20 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-21</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr">
+      <c r="L227" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L227" t="inlineStr">
+      <c r="M227" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13679,15 +14814,20 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ankersen ApS</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-21</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr">
+      <c r="L228" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L228" t="inlineStr">
+      <c r="M228" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13739,15 +14879,20 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ankersen ApS</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-08</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr">
+      <c r="L229" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L229" t="inlineStr">
+      <c r="M229" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13799,15 +14944,20 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ankersen ApS</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-08</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr">
+      <c r="L230" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L230" t="inlineStr">
+      <c r="M230" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13859,15 +15009,20 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ankersen ApS</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-08</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr">
+      <c r="L231" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L231" t="inlineStr">
+      <c r="M231" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13919,15 +15074,20 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ankersen ApS</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-08</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr">
+      <c r="L232" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L232" t="inlineStr">
+      <c r="M232" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13979,15 +15139,20 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
+          <t xml:space="preserve">Inspec ApS</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-20</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr">
+      <c r="L233" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L233" t="inlineStr">
+      <c r="M233" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14039,15 +15204,20 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr">
+      <c r="L234" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L234" t="inlineStr">
+      <c r="M234" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14099,15 +15269,20 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr">
+      <c r="L235" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L235" t="inlineStr">
+      <c r="M235" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14159,15 +15334,20 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr">
+      <c r="L236" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L236" t="inlineStr">
+      <c r="M236" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14219,15 +15399,20 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr">
+      <c r="L237" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L237" t="inlineStr">
+      <c r="M237" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14279,15 +15464,20 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr">
+      <c r="L238" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L238" t="inlineStr">
+      <c r="M238" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14339,15 +15529,20 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ankersen ApS</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr">
+      <c r="L239" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L239" t="inlineStr">
+      <c r="M239" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14399,15 +15594,20 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr">
+      <c r="L240" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L240" t="inlineStr">
+      <c r="M240" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14459,15 +15659,20 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr">
+      <c r="L241" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L241" t="inlineStr">
+      <c r="M241" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14519,21 +15724,26 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bedre Bolig Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-10</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr">
+      <c r="L242" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L242" t="inlineStr">
+      <c r="M242" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L242"/>
+  <autoFilter ref="A1:M242"/>
 </worksheet>
 </file>
--- a/public/exports/29189609.xlsx
+++ b/public/exports/29189609.xlsx
@@ -13574,12 +13574,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311419880</t>
+          <t xml:space="preserve">311419877</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Scanenergi A/S</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
